--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -857,112 +857,112 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G2" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="H2" t="n">
         <v>7.2</v>
       </c>
       <c r="I2" t="n">
+        <v>970</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K2" t="n">
         <v>15</v>
       </c>
-      <c r="J2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>1.71</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>1.01</v>
@@ -1019,58 +1019,58 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.9</v>
+        <v>1.32</v>
       </c>
       <c r="BP2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BR2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BT2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,19 +1135,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
         <v>2.22</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
         <v>2.22</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,19 +1389,19 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
         <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
         <v>3.4</v>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1476,25 +1476,25 @@
         <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
         <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
         <v>1.01</v>
@@ -1503,22 +1503,22 @@
         <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1527,68 +1527,68 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI4" t="n">
         <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>1.34</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>1.34</v>
       </c>
       <c r="BN4" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.5</v>
+        <v>1.34</v>
       </c>
       <c r="BP4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>18.5</v>
+        <v>1.34</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>21</v>
+        <v>1.34</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="BV4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>1.34</v>
       </c>
       <c r="BX4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>18.5</v>
+        <v>1.34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>16.5</v>
+        <v>1.34</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.89</v>
@@ -1631,22 +1631,22 @@
         <v>2.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.74</v>
@@ -1655,184 +1655,184 @@
         <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I6" t="n">
         <v>2.22</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.7</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
         <v>5.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>2.78</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
         <v>2.66</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
         <v>1.57</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="I12" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="H17" t="n">
-        <v>2.86</v>
+        <v>1.59</v>
       </c>
       <c r="I17" t="n">
         <v>3.25</v>
@@ -4682,7 +4682,7 @@
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H19" t="n">
         <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
         <v>5.4</v>
@@ -5462,7 +5462,7 @@
         <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -5686,16 +5686,16 @@
         <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H21" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I21" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>3.95</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="G26" t="n">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
         <v>1.01</v>
@@ -6965,7 +6965,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>2.72</v>
       </c>
       <c r="G29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H29" t="n">
         <v>2.26</v>
       </c>
       <c r="I29" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="G30" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,10 +7999,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
         <v>3.9</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H32" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -8731,22 +8731,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -8985,19 +8985,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="G34" t="n">
         <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I34" t="n">
         <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
         <v>6.8</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="G35" t="n">
         <v>2.02</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q35" t="n">
         <v>1.74</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G37" t="n">
         <v>1.43</v>
       </c>
       <c r="H37" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="I37" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="J37" t="n">
         <v>5.6</v>
       </c>
       <c r="K37" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q37" t="n">
         <v>1.33</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -10001,22 +10001,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="G38" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H38" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="I38" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -10258,227 +10258,227 @@
         <v>1.55</v>
       </c>
       <c r="G39" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H39" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="J39" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="O39" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P39" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q39" t="n">
         <v>1.98</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="T39" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
         <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X39" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ39" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN39" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP39" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR39" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT39" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -10509,28 +10509,28 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G40" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="I40" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -10539,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
         <v>1.96</v>
@@ -10551,10 +10551,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U40" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -10563,112 +10563,112 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE40" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG40" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G41" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H41" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="I41" t="n">
         <v>11.5</v>
@@ -10778,7 +10778,7 @@
         <v>5.2</v>
       </c>
       <c r="K41" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.54</v>
+        <v>1.02</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10805,10 +10805,10 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -11017,22 +11017,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G42" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="H42" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="J42" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11059,7 +11059,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
         <v>2.16</v>
@@ -11071,112 +11071,112 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="n">
         <v>0</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -11271,28 +11271,28 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G43" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H43" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="J43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K43" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -11301,7 +11301,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
         <v>2.1</v>
@@ -11313,10 +11313,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -11325,112 +11325,112 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -11531,16 +11531,16 @@
         <v>1.65</v>
       </c>
       <c r="H44" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q44" t="n">
         <v>1.66</v>
@@ -11567,10 +11567,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U44" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -11579,112 +11579,112 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE44" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR44" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT44" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX44" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA44" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB44" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC44" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG44" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH44" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -12033,28 +12033,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H46" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I46" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J46" t="n">
         <v>3.55</v>
       </c>
       <c r="K46" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -12087,112 +12087,112 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>2.62</v>
       </c>
       <c r="G50" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H50" t="n">
         <v>2.74</v>
@@ -13061,7 +13061,7 @@
         <v>3.1</v>
       </c>
       <c r="J50" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K50" t="n">
         <v>3.65</v>
@@ -13082,7 +13082,7 @@
         <v>1.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
         <v>2.52</v>
       </c>
       <c r="H51" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="I51" t="n">
         <v>3.9</v>
@@ -13318,13 +13318,13 @@
         <v>2.88</v>
       </c>
       <c r="K51" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.14</v>
+        <v>1.08</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -13557,166 +13557,166 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="G52" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="I52" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="J52" t="n">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="K52" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O52" t="n">
         <v>1.39</v>
       </c>
       <c r="P52" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W52" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X52" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -13814,16 +13814,16 @@
         <v>3.1</v>
       </c>
       <c r="G53" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H53" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I53" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K53" t="n">
         <v>3.9</v>
@@ -13844,7 +13844,7 @@
         <v>1.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -14065,28 +14065,28 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G54" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H54" t="n">
         <v>6.2</v>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J54" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K54" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -14095,10 +14095,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.02</v>
+        <v>1.91</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -14107,10 +14107,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
@@ -14200,7 +14200,7 @@
         <v>1.01</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -14319,19 +14319,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G55" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H55" t="n">
         <v>3.4</v>
       </c>
       <c r="I55" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K55" t="n">
         <v>3.95</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -14349,7 +14349,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q55" t="n">
         <v>1.84</v>
@@ -14361,10 +14361,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -14373,112 +14373,112 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z55" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI55" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO55" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV55" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX55" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB55" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE55" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14585,7 @@
         <v>5.9</v>
       </c>
       <c r="J56" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="K56" t="n">
         <v>3.5</v>
@@ -14597,10 +14597,10 @@
         <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>1.29</v>
+        <v>2.46</v>
       </c>
       <c r="O56" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P56" t="n">
         <v>1.28</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G57" t="n">
         <v>2.32</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G59" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I59" t="n">
         <v>17.5</v>
@@ -15350,7 +15350,7 @@
         <v>6.8</v>
       </c>
       <c r="K59" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15365,10 +15365,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -15595,10 +15595,10 @@
         <v>2.06</v>
       </c>
       <c r="H60" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I60" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -15607,13 +15607,13 @@
         <v>3.55</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M60" t="n">
         <v>1.12</v>
       </c>
       <c r="N60" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="O60" t="n">
         <v>1.56</v>
@@ -15622,7 +15622,7 @@
         <v>1.47</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R60" t="n">
         <v>1.17</v>
@@ -15637,7 +15637,7 @@
         <v>1.62</v>
       </c>
       <c r="V60" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W60" t="n">
         <v>1.94</v>
@@ -15646,7 +15646,7 @@
         <v>9.4</v>
       </c>
       <c r="Y60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z60" t="n">
         <v>50</v>
@@ -15658,7 +15658,7 @@
         <v>7</v>
       </c>
       <c r="AC60" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD60" t="n">
         <v>28</v>
@@ -15697,58 +15697,58 @@
         <v>260</v>
       </c>
       <c r="AP60" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX60" t="n">
         <v>3.55</v>
       </c>
-      <c r="AQ60" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR60" t="n">
+      <c r="AY60" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE60" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS60" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF60" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BG60" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH60" t="n">
         <v>2.72</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -15873,7 +15873,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q61" t="n">
         <v>1.01</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -16097,22 +16097,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.46</v>
+        <v>2.34</v>
       </c>
       <c r="G62" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H62" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="I62" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J62" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="K62" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -16127,10 +16127,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -16351,118 +16351,118 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G63" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="H63" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I63" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J63" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K63" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M63" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N63" t="n">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="O63" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P63" t="n">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R63" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="T63" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W63" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="X63" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y63" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z63" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA63" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC63" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD63" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE63" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF63" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG63" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH63" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI63" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK63" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL63" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM63" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO63" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP63" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ63" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR63" t="n">
         <v>1.01</v>
@@ -16471,110 +16471,110 @@
         <v>1.01</v>
       </c>
       <c r="AT63" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU63" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV63" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW63" t="n">
         <v>1.01</v>
       </c>
       <c r="AX63" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY63" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ63" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA63" t="n">
         <v>1.01</v>
       </c>
       <c r="BB63" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE63" t="n">
         <v>1.01</v>
       </c>
       <c r="BF63" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG63" t="n">
         <v>1.01</v>
       </c>
       <c r="BH63" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI63" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ63" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK63" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BN63" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO63" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP63" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR63" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT63" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU63" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV63" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX63" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ63" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA63" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.05</v>
+        <v>1.68</v>
       </c>
       <c r="Q64" t="n">
         <v>2.1</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -16862,13 +16862,13 @@
         <v>1.93</v>
       </c>
       <c r="G65" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H65" t="n">
         <v>4.1</v>
       </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>3.3</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -17113,19 +17113,19 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G66" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H66" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I66" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="J66" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K66" t="n">
         <v>4.6</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="G67" t="n">
         <v>2.02</v>
@@ -17379,34 +17379,34 @@
         <v>7.2</v>
       </c>
       <c r="J67" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K67" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="O67" t="n">
         <v>1.2</v>
       </c>
       <c r="P67" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R67" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S67" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="T67" t="n">
         <v>1.01</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -17621,22 +17621,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="G68" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="J68" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K68" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -17651,10 +17651,10 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -17878,10 +17878,10 @@
         <v>2.54</v>
       </c>
       <c r="G69" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H69" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I69" t="n">
         <v>3.9</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -18132,19 +18132,19 @@
         <v>2.12</v>
       </c>
       <c r="G70" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H70" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I70" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K70" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -18162,7 +18162,7 @@
         <v>1.75</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -18401,7 +18401,7 @@
         <v>3.65</v>
       </c>
       <c r="L71" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M71" t="n">
         <v>1.08</v>
@@ -18413,7 +18413,7 @@
         <v>1.36</v>
       </c>
       <c r="P71" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q71" t="n">
         <v>2.08</v>
@@ -18491,7 +18491,7 @@
         <v>30</v>
       </c>
       <c r="AP71" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ71" t="n">
         <v>8.4</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18661,7 @@
         <v>1.1</v>
       </c>
       <c r="N72" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="O72" t="n">
         <v>1.43</v>
@@ -18676,7 +18676,7 @@
         <v>1.22</v>
       </c>
       <c r="S72" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
         <v>1.91</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-29 05:02:11</t>
+          <t>2026-05-29 07:28:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB83"/>
+  <dimension ref="A1:CB84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,7 +1022,7 @@
         <v>3.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ2" t="n">
         <v>14.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1395,10 +1395,10 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -1413,13 +1413,13 @@
         <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1470,16 +1470,16 @@
         <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="n">
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.18</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="n">
         <v>2.22</v>
@@ -1888,7 +1888,7 @@
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1915,7 +1915,7 @@
         <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
         <v>1.11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
         <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
         <v>1.56</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -2417,10 +2417,10 @@
         <v>1.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>1.65</v>
       </c>
       <c r="G9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -2683,7 +2683,7 @@
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
         <v>2.28</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.7</v>
@@ -3173,7 +3173,7 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>2.06</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.27</v>
@@ -3430,55 +3430,55 @@
         <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
         <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
         <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
         <v>14.5</v>
@@ -3490,19 +3490,19 @@
         <v>70</v>
       </c>
       <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
         <v>40</v>
       </c>
-      <c r="AL12" t="n">
-        <v>44</v>
-      </c>
       <c r="AM12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
         <v>28</v>
       </c>
       <c r="AO12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP12" t="n">
         <v>17.5</v>
@@ -3517,43 +3517,43 @@
         <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
         <v>14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
         <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>9.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
@@ -3681,13 +3681,13 @@
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
         <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
         <v>2.96</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -4183,16 +4183,16 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
         <v>1.13</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>1.24</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H16" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="I16" t="n">
         <v>3.35</v>
       </c>
       <c r="J16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4443,10 +4443,10 @@
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R16" t="n">
         <v>1.14</v>
@@ -4461,7 +4461,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
         <v>1.41</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
         <v>2.9</v>
@@ -4694,7 +4694,7 @@
         <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
         <v>2.22</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q18" t="n">
         <v>1.25</v>
@@ -4960,7 +4960,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
         <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5737,7 +5737,7 @@
         <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
         <v>23</v>
@@ -5797,10 +5797,10 @@
         <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT21" t="n">
         <v>5.8</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>2.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H22" t="n">
         <v>2.54</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
         <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>1.57</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G24" t="n">
         <v>2.3</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="O28" t="n">
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Q28" t="n">
         <v>1.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
         <v>3.95</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H30" t="n">
         <v>4.8</v>
@@ -7981,7 +7981,7 @@
         <v>5.9</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
         <v>4.1</v>
@@ -7990,10 +7990,10 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
         <v>1.27</v>
@@ -8008,13 +8008,13 @@
         <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U30" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="V30" t="n">
         <v>1.2</v>
@@ -8023,112 +8023,112 @@
         <v>2.12</v>
       </c>
       <c r="X30" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG30" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK30" t="n">
         <v>22</v>
       </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP30" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
         <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
         <v>1.76</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>2.98</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R32" t="n">
         <v>1.77</v>
@@ -8519,7 +8519,7 @@
         <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
         <v>2.68</v>
       </c>
       <c r="O33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
         <v>2.68</v>
@@ -8767,16 +8767,16 @@
         <v>1.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S33" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T33" t="n">
         <v>1.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V33" t="n">
         <v>1.64</v>
@@ -8785,112 +8785,112 @@
         <v>1.47</v>
       </c>
       <c r="X33" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA33" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG33" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI33" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK33" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY33" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G34" t="n">
         <v>1.45</v>
@@ -9021,7 +9021,7 @@
         <v>1.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="S34" t="n">
         <v>1.87</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -9263,13 +9263,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>1.13</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
         <v>1.45</v>
@@ -9278,7 +9278,7 @@
         <v>1.6</v>
       </c>
       <c r="S35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="G36" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="H36" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
         <v>5.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9523,16 +9523,16 @@
         <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R36" t="n">
         <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T36" t="n">
         <v>1.11</v>
@@ -9544,7 +9544,7 @@
         <v>1.22</v>
       </c>
       <c r="W36" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O37" t="n">
         <v>1.23</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
         <v>1.54</v>
       </c>
       <c r="R38" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S38" t="n">
         <v>2.3</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>870</v>
       </c>
       <c r="J39" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K39" t="n">
         <v>950</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>2.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H40" t="n">
         <v>2.72</v>
       </c>
       <c r="I40" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>1.56</v>
       </c>
       <c r="G41" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H41" t="n">
         <v>6.6</v>
@@ -10781,7 +10781,7 @@
         <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
@@ -10814,7 +10814,7 @@
         <v>1.14</v>
       </c>
       <c r="W41" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X41" t="n">
         <v>16</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -11020,19 +11020,19 @@
         <v>1.38</v>
       </c>
       <c r="G42" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H42" t="n">
         <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K42" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11062,13 +11062,13 @@
         <v>1.84</v>
       </c>
       <c r="U42" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
         <v>1.09</v>
       </c>
       <c r="W42" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X42" t="n">
         <v>25</v>
@@ -11080,7 +11080,7 @@
         <v>95</v>
       </c>
       <c r="AA42" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="AB42" t="n">
         <v>11</v>
@@ -11089,10 +11089,10 @@
         <v>13</v>
       </c>
       <c r="AD42" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE42" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF42" t="n">
         <v>9.800000000000001</v>
@@ -11107,7 +11107,7 @@
         <v>120</v>
       </c>
       <c r="AJ42" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK42" t="n">
         <v>14</v>
@@ -11122,19 +11122,19 @@
         <v>5.1</v>
       </c>
       <c r="AO42" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AR42" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AT42" t="n">
         <v>9.4</v>
@@ -11158,7 +11158,7 @@
         <v>22</v>
       </c>
       <c r="BA42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB42" t="n">
         <v>9.6</v>
@@ -11170,7 +11170,7 @@
         <v>27</v>
       </c>
       <c r="BE42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF42" t="n">
         <v>4.4</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -11271,10 +11271,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G43" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H43" t="n">
         <v>6.8</v>
@@ -11322,7 +11322,7 @@
         <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X43" t="n">
         <v>15.5</v>
@@ -11343,7 +11343,7 @@
         <v>10.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE43" t="n">
         <v>130</v>
@@ -11391,7 +11391,7 @@
         <v>10</v>
       </c>
       <c r="AT43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU43" t="n">
         <v>9</v>
@@ -11412,7 +11412,7 @@
         <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB43" t="n">
         <v>12.5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -11525,19 +11525,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="G44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H44" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="I44" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="J44" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
         <v>3.6</v>
@@ -11549,52 +11549,52 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P44" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T44" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="U44" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V44" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="W44" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X44" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD44" t="n">
         <v>12</v>
@@ -11603,64 +11603,64 @@
         <v>24</v>
       </c>
       <c r="AF44" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG44" t="n">
         <v>21</v>
       </c>
       <c r="AH44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI44" t="n">
         <v>46</v>
       </c>
       <c r="AJ44" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK44" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AL44" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AM44" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN44" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO44" t="n">
         <v>17.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ44" t="n">
         <v>7.2</v>
       </c>
       <c r="AR44" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS44" t="n">
         <v>19</v>
       </c>
       <c r="AT44" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU44" t="n">
         <v>7.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW44" t="n">
         <v>19</v>
       </c>
       <c r="AX44" t="n">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="AY44" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>18</v>
@@ -11669,22 +11669,22 @@
         <v>36</v>
       </c>
       <c r="BB44" t="n">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC44" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD44" t="n">
         <v>55</v>
       </c>
       <c r="BE44" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -11782,16 +11782,16 @@
         <v>1.42</v>
       </c>
       <c r="G45" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="H45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I45" t="n">
         <v>8.4</v>
       </c>
       <c r="J45" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K45" t="n">
         <v>5.8</v>
@@ -11803,10 +11803,10 @@
         <v>1.03</v>
       </c>
       <c r="N45" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P45" t="n">
         <v>2.56</v>
@@ -11818,7 +11818,7 @@
         <v>1.61</v>
       </c>
       <c r="S45" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T45" t="n">
         <v>1.81</v>
@@ -11830,7 +11830,7 @@
         <v>1.13</v>
       </c>
       <c r="W45" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X45" t="n">
         <v>28</v>
@@ -11884,7 +11884,7 @@
         <v>6.6</v>
       </c>
       <c r="AO45" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP45" t="n">
         <v>22</v>
@@ -11896,19 +11896,19 @@
         <v>8.4</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT45" t="n">
         <v>9.4</v>
       </c>
       <c r="AU45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV45" t="n">
         <v>26</v>
       </c>
       <c r="AW45" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX45" t="n">
         <v>9</v>
@@ -11932,16 +11932,16 @@
         <v>25</v>
       </c>
       <c r="BE45" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF45" t="n">
         <v>5</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BH45" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI45" t="n">
         <v>3.05</v>
@@ -11950,13 +11950,13 @@
         <v>15</v>
       </c>
       <c r="BK45" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BN45" t="n">
         <v>5.9</v>
@@ -11974,42 +11974,42 @@
         <v>30</v>
       </c>
       <c r="BS45" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BT45" t="n">
         <v>16</v>
       </c>
       <c r="BU45" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BZ45" t="n">
         <v>17.5</v>
       </c>
       <c r="CA45" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12024,115 +12024,115 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="G46" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="H46" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K46" t="n">
         <v>3.8</v>
       </c>
-      <c r="K46" t="n">
-        <v>4</v>
-      </c>
       <c r="L46" t="n">
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P46" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="R46" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="X46" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y46" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z46" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC46" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD46" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE46" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG46" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH46" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI46" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK46" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL46" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
         <v>1000</v>
@@ -12141,58 +12141,58 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.36</v>
+        <v>1.03</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.18</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.48</v>
+        <v>1.03</v>
       </c>
       <c r="AX46" t="n">
-        <v>2.48</v>
+        <v>1.03</v>
       </c>
       <c r="AY46" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="BB46" t="n">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.56</v>
+        <v>1.03</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>1.6</v>
       </c>
       <c r="G47" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H47" t="n">
         <v>5.5</v>
@@ -12299,16 +12299,16 @@
         <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N47" t="n">
         <v>5.4</v>
@@ -12329,13 +12329,13 @@
         <v>2.44</v>
       </c>
       <c r="T47" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="U47" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V47" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W47" t="n">
         <v>2.52</v>
@@ -12344,7 +12344,7 @@
         <v>30</v>
       </c>
       <c r="Y47" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z47" t="n">
         <v>60</v>
@@ -12353,7 +12353,7 @@
         <v>160</v>
       </c>
       <c r="AB47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC47" t="n">
         <v>13.5</v>
@@ -12365,7 +12365,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG47" t="n">
         <v>12.5</v>
@@ -12398,13 +12398,13 @@
         <v>21</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR47" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT47" t="n">
         <v>10</v>
@@ -12416,7 +12416,7 @@
         <v>19</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX47" t="n">
         <v>8.800000000000001</v>
@@ -12428,7 +12428,7 @@
         <v>16</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB47" t="n">
         <v>12</v>
@@ -12437,16 +12437,16 @@
         <v>11</v>
       </c>
       <c r="BD47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF47" t="n">
         <v>5</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12532,246 +12532,246 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="G48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J48" t="n">
         <v>3.75</v>
       </c>
-      <c r="H48" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K48" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.65</v>
       </c>
-      <c r="L48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O48" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="P48" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="R48" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="V48" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="W48" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X48" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Y48" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Z48" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AA48" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE48" t="n">
         <v>32</v>
       </c>
-      <c r="AB48" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE48" t="n">
+      <c r="AF48" t="n">
         <v>30</v>
       </c>
-      <c r="AF48" t="n">
-        <v>25</v>
-      </c>
       <c r="AG48" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH48" t="n">
         <v>21</v>
       </c>
       <c r="AI48" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ48" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK48" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM48" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN48" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>11</v>
+        <v>2.42</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="AR48" t="n">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>8</v>
+        <v>2.54</v>
       </c>
       <c r="AT48" t="n">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="AU48" t="n">
-        <v>7.2</v>
+        <v>2.18</v>
       </c>
       <c r="AV48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AY48" t="n">
         <v>10</v>
       </c>
-      <c r="AW48" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ48" t="n">
-        <v>18</v>
+        <v>2.38</v>
       </c>
       <c r="BA48" t="n">
-        <v>38</v>
+        <v>2.54</v>
       </c>
       <c r="BB48" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>40</v>
+        <v>2.54</v>
       </c>
       <c r="BD48" t="n">
-        <v>50</v>
+        <v>2.56</v>
       </c>
       <c r="BE48" t="n">
-        <v>9.800000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="BF48" t="n">
-        <v>8.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>18</v>
+        <v>2.7</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
       </c>
       <c r="BI48" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BJ48" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK48" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BN48" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO48" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP48" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BT48" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU48" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV48" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW48" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BX48" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,239 +12786,239 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="G49" t="n">
-        <v>2.86</v>
+        <v>3.75</v>
       </c>
       <c r="H49" t="n">
-        <v>2.68</v>
+        <v>2.18</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="J49" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K49" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M49" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X49" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>44</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU49" t="n">
         <v>3.4</v>
       </c>
-      <c r="O49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU49" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BX49" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>110</v>
       </c>
       <c r="J53" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K53" t="n">
         <v>950</v>
@@ -13835,7 +13835,7 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O53" t="n">
         <v>1.01</v>
@@ -13850,7 +13850,7 @@
         <v>1.12</v>
       </c>
       <c r="S53" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
         <v>870</v>
       </c>
       <c r="J54" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K54" t="n">
         <v>950</v>
@@ -14098,13 +14098,13 @@
         <v>1.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R54" t="n">
         <v>1.12</v>
       </c>
       <c r="S54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
         <v>3.4</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>3.4</v>
@@ -14337,28 +14337,28 @@
         <v>3.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M55" t="n">
         <v>1.08</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O55" t="n">
         <v>1.38</v>
       </c>
       <c r="P55" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
         <v>2.12</v>
       </c>
       <c r="R55" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S55" t="n">
-        <v>2.46</v>
+        <v>3.8</v>
       </c>
       <c r="T55" t="n">
         <v>1.68</v>
@@ -14367,7 +14367,7 @@
         <v>1.76</v>
       </c>
       <c r="V55" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W55" t="n">
         <v>1.71</v>
@@ -14484,19 +14484,19 @@
         <v>1000</v>
       </c>
       <c r="BI55" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BJ55" t="n">
         <v>15</v>
       </c>
       <c r="BK55" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BN55" t="n">
         <v>6.8</v>
@@ -14508,13 +14508,13 @@
         <v>25</v>
       </c>
       <c r="BQ55" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BR55" t="n">
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BT55" t="n">
         <v>9.800000000000001</v>
@@ -14526,23 +14526,23 @@
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
         <v>1.25</v>
       </c>
       <c r="S56" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T56" t="n">
         <v>1.11</v>
@@ -14621,7 +14621,7 @@
         <v>1.8</v>
       </c>
       <c r="V56" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W56" t="n">
         <v>1.51</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
         <v>110</v>
       </c>
       <c r="J58" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K58" t="n">
         <v>950</v>
@@ -15114,13 +15114,13 @@
         <v>1.24</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R58" t="n">
         <v>1.12</v>
       </c>
       <c r="S58" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
         <v>110</v>
       </c>
       <c r="J59" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K59" t="n">
         <v>950</v>
@@ -15368,13 +15368,13 @@
         <v>1.24</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R59" t="n">
         <v>1.12</v>
       </c>
       <c r="S59" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="T59" t="n">
         <v>1.01</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -15589,22 +15589,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="G60" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J60" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="K60" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15613,13 +15613,13 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O60" t="n">
         <v>1.19</v>
       </c>
       <c r="P60" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q60" t="n">
         <v>1.6</v>
@@ -15637,10 +15637,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W60" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,176 +15834,176 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="G61" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="H61" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="I61" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S61" t="n">
         <v>3.35</v>
       </c>
-      <c r="K61" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3.05</v>
-      </c>
       <c r="T61" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U61" t="n">
         <v>2.12</v>
       </c>
       <c r="V61" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="W61" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="X61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y61" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Z61" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI61" t="n">
         <v>46</v>
       </c>
-      <c r="AA61" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF61" t="n">
+      <c r="AJ61" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR61" t="n">
         <v>12</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AS61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV61" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH61" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN61" t="n">
+      <c r="AW61" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG61" t="n">
         <v>14</v>
       </c>
-      <c r="AO61" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>46</v>
-      </c>
       <c r="BH61" t="n">
         <v>1000</v>
       </c>
@@ -16011,7 +16011,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ61" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK61" t="n">
         <v>1.01</v>
@@ -16023,28 +16023,28 @@
         <v>1.01</v>
       </c>
       <c r="BN61" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO61" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP61" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ61" t="n">
         <v>1.01</v>
       </c>
       <c r="BR61" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS61" t="n">
         <v>1.01</v>
       </c>
       <c r="BT61" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU61" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV61" t="n">
         <v>1000</v>
@@ -16059,21 +16059,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ61" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA61" t="n">
         <v>1.01</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16088,175 +16088,175 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="G62" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="H62" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="I62" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K62" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L62" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
         <v>1.06</v>
       </c>
       <c r="N62" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O62" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P62" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R62" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S62" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T62" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U62" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V62" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="W62" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="X62" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA62" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE62" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI62" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK62" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL62" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM62" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN62" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO62" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU62" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -16342,31 +16342,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="G63" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="H63" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="I63" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="J63" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K63" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -16381,200 +16381,200 @@
         <v>1.29</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R63" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S63" t="n">
         <v>3.2</v>
       </c>
       <c r="T63" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U63" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W63" t="n">
         <v>2.2</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.79</v>
-      </c>
       <c r="X63" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y63" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z63" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AA63" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AB63" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BT63" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC63" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA63" t="n">
+      <c r="BU63" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB63" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV63" t="n">
         <v>1000</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -16608,7 +16608,7 @@
         <v>1.94</v>
       </c>
       <c r="G64" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H64" t="n">
         <v>4.6</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
         <v>2.02</v>
       </c>
       <c r="G65" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H65" t="n">
         <v>4.3</v>
@@ -16877,16 +16877,16 @@
         <v>3.5</v>
       </c>
       <c r="L65" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M65" t="n">
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>2.74</v>
+        <v>1.59</v>
       </c>
       <c r="O65" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P65" t="n">
         <v>1.59</v>
@@ -16910,7 +16910,7 @@
         <v>1.25</v>
       </c>
       <c r="W65" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X65" t="n">
         <v>13</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
         <v>1.28</v>
       </c>
       <c r="G66" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H66" t="n">
         <v>12</v>
@@ -17128,7 +17128,7 @@
         <v>6.6</v>
       </c>
       <c r="K66" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -17367,10 +17367,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G67" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H67" t="n">
         <v>3.6</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -17621,13 +17621,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G68" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H68" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I68" t="n">
         <v>6.8</v>
@@ -17648,7 +17648,7 @@
         <v>1.38</v>
       </c>
       <c r="O68" t="n">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="P68" t="n">
         <v>1.38</v>
@@ -17663,25 +17663,25 @@
         <v>2.52</v>
       </c>
       <c r="T68" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U68" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V68" t="n">
         <v>1.17</v>
       </c>
       <c r="W68" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X68" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y68" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA68" t="n">
         <v>210</v>
@@ -17702,7 +17702,7 @@
         <v>11.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH68" t="n">
         <v>34</v>
@@ -17711,25 +17711,25 @@
         <v>160</v>
       </c>
       <c r="AJ68" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK68" t="n">
         <v>34</v>
       </c>
       <c r="AL68" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM68" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN68" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO68" t="n">
         <v>250</v>
       </c>
       <c r="AP68" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ68" t="n">
         <v>10</v>
@@ -17756,7 +17756,7 @@
         <v>7.8</v>
       </c>
       <c r="AY68" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ68" t="n">
         <v>21</v>
@@ -17765,7 +17765,7 @@
         <v>5.1</v>
       </c>
       <c r="BB68" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC68" t="n">
         <v>21</v>
@@ -17777,16 +17777,16 @@
         <v>5.1</v>
       </c>
       <c r="BF68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG68" t="n">
         <v>5.1</v>
       </c>
       <c r="BH68" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BI68" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ68" t="n">
         <v>13</v>
@@ -17798,13 +17798,13 @@
         <v>1000</v>
       </c>
       <c r="BM68" t="n">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="BN68" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO68" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP68" t="n">
         <v>16.5</v>
@@ -17816,10 +17816,10 @@
         <v>1000</v>
       </c>
       <c r="BS68" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT68" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU68" t="n">
         <v>4.9</v>
@@ -17834,17 +17834,17 @@
         <v>1000</v>
       </c>
       <c r="BY68" t="n">
-        <v>3.05</v>
+        <v>9.6</v>
       </c>
       <c r="BZ68" t="n">
         <v>1000</v>
       </c>
       <c r="CA68" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -17983,52 +17983,52 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE69" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF69" t="n">
         <v>1.01</v>
@@ -18098,14 +18098,14 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -18120,246 +18120,246 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="G70" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="H70" t="n">
-        <v>2.76</v>
+        <v>1.68</v>
       </c>
       <c r="I70" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K70" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P70" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -18369,251 +18369,251 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CD Los Chankas</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UTC Cajamarca</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="G71" t="n">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="H71" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="J71" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="K71" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L71" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="O71" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P71" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="R71" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S71" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="T71" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U71" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V71" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W71" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="X71" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y71" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z71" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA71" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB71" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC71" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD71" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE71" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF71" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG71" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH71" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI71" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ71" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK71" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL71" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM71" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN71" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO71" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ71" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR71" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS71" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT71" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU71" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV71" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW71" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX71" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AY71" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ71" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA71" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB71" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC71" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD71" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE71" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF71" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG71" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH71" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI71" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="BJ71" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>5.3</v>
+        <v>1.37</v>
       </c>
       <c r="BL71" t="n">
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>10</v>
+        <v>1.37</v>
       </c>
       <c r="BN71" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>3.4</v>
+        <v>1.37</v>
       </c>
       <c r="BP71" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>5.8</v>
+        <v>1.37</v>
       </c>
       <c r="BR71" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>7.8</v>
+        <v>1.37</v>
       </c>
       <c r="BT71" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>4.9</v>
+        <v>1.37</v>
       </c>
       <c r="BV71" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>8.6</v>
+        <v>1.37</v>
       </c>
       <c r="BX71" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>9</v>
+        <v>1.37</v>
       </c>
       <c r="BZ71" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA71" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -18623,251 +18623,251 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>CD Los Chankas</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>UTC Cajamarca</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5.6</v>
+        <v>1.77</v>
       </c>
       <c r="G72" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X72" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY72" t="n">
         <v>7.4</v>
       </c>
-      <c r="H72" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I72" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J72" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K72" t="n">
+      <c r="AZ72" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE72" t="n">
         <v>4.1</v>
       </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE72" t="n">
-        <v>0</v>
-      </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG72" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BJ72" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK72" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BL72" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BN72" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP72" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ72" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BR72" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS72" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BT72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU72" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV72" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BW72" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BX72" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ72" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA72" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -18877,244 +18877,244 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Deportivo Tachira</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Independiente (Ecu)</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.33</v>
+        <v>5.6</v>
       </c>
       <c r="G73" t="n">
-        <v>1.46</v>
+        <v>7.4</v>
       </c>
       <c r="H73" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>1.84</v>
       </c>
       <c r="J73" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K73" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P73" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE73" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -19136,229 +19136,229 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Deportivo Tachira</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="F74" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I74" t="n">
+        <v>29</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S74" t="n">
         <v>2.6</v>
       </c>
-      <c r="G74" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I74" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K74" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH74" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI74" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX74" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ74" t="n">
         <v>0</v>
@@ -19368,14 +19368,14 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -19385,234 +19385,234 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="G75" t="n">
-        <v>2.12</v>
+        <v>3.35</v>
       </c>
       <c r="H75" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="J75" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="K75" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P75" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX75" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY75" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ75" t="n">
         <v>0</v>
@@ -19622,14 +19622,14 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -19644,109 +19644,109 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Everton De Vina</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.25</v>
+        <v>1.93</v>
       </c>
       <c r="G76" t="n">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="H76" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="I76" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="J76" t="n">
         <v>3.4</v>
       </c>
       <c r="K76" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L76" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M76" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N76" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O76" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R76" t="n">
         <v>1.29</v>
       </c>
-      <c r="P76" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R76" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S76" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="T76" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="U76" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V76" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="W76" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
       </c>
       <c r="Y76" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG76" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z76" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>20</v>
-      </c>
       <c r="AH76" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI76" t="n">
         <v>1000</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK76" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL76" t="n">
         <v>1000</v>
@@ -19764,7 +19764,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ76" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR76" t="n">
         <v>1.03</v>
@@ -19773,34 +19773,34 @@
         <v>1.03</v>
       </c>
       <c r="AT76" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AU76" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY76" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ76" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA76" t="n">
         <v>1.03</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BC76" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BD76" t="n">
         <v>1.03</v>
@@ -19876,14 +19876,14 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -19893,251 +19893,251 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Nacional (Uru)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="G77" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H77" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="J77" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K77" t="n">
-        <v>830</v>
+        <v>4.5</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P77" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU77" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AW77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE77" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ77" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -20152,55 +20152,55 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cienciano</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="G78" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="H78" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I78" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="K78" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L78" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M78" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="O78" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P78" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R78" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -20209,10 +20209,10 @@
         <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W78" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -20269,52 +20269,52 @@
         <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF78" t="n">
         <v>1.01</v>
@@ -20323,75 +20323,75 @@
         <v>1.01</v>
       </c>
       <c r="BH78" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI78" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ78" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK78" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL78" t="n">
         <v>1000</v>
       </c>
       <c r="BM78" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN78" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO78" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP78" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ78" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR78" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS78" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT78" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU78" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV78" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW78" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX78" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY78" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ78" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA78" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -20401,251 +20401,251 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="G79" t="n">
-        <v>3.4</v>
+        <v>1.89</v>
       </c>
       <c r="H79" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="I79" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI79" t="n">
         <v>3.15</v>
       </c>
-      <c r="J79" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K79" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI79" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ79" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK79" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL79" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM79" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BN79" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BO79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP79" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BQ79" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BR79" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BS79" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BT79" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU79" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV79" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW79" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX79" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY79" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BZ79" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA79" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -20655,36 +20655,36 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="G80" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="H80" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="I80" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="J80" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -20699,10 +20699,10 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -20926,10 +20926,10 @@
         <v>2.1</v>
       </c>
       <c r="G81" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H81" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I81" t="n">
         <v>4.3</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
@@ -21195,7 +21195,7 @@
         <v>3.5</v>
       </c>
       <c r="L82" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M82" t="n">
         <v>1.08</v>
@@ -21300,7 +21300,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU82" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV82" t="n">
         <v>9</v>
@@ -21400,261 +21400,515 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-29 17:24:24</t>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K83" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB83" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:49:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>Brazilian Serie C</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Figueirense</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Paysandu</t>
         </is>
       </c>
-      <c r="F83" t="n">
+      <c r="F84" t="n">
         <v>2.52</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G84" t="n">
         <v>2.92</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H84" t="n">
         <v>2.92</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I84" t="n">
         <v>3.4</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J84" t="n">
         <v>3</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K84" t="n">
         <v>3.5</v>
       </c>
-      <c r="L83" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M83" t="n">
+      <c r="L84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M84" t="n">
         <v>1.1</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N84" t="n">
         <v>2.82</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O84" t="n">
         <v>1.43</v>
       </c>
-      <c r="P83" t="n">
+      <c r="P84" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q84" t="n">
         <v>2.28</v>
       </c>
-      <c r="R83" t="n">
+      <c r="R84" t="n">
         <v>1.23</v>
       </c>
-      <c r="S83" t="n">
+      <c r="S84" t="n">
         <v>4.4</v>
       </c>
-      <c r="T83" t="n">
+      <c r="T84" t="n">
         <v>1.91</v>
       </c>
-      <c r="U83" t="n">
+      <c r="U84" t="n">
         <v>1.88</v>
       </c>
-      <c r="V83" t="n">
+      <c r="V84" t="n">
         <v>1.41</v>
       </c>
-      <c r="W83" t="n">
+      <c r="W84" t="n">
         <v>1.52</v>
       </c>
-      <c r="X83" t="n">
+      <c r="X84" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="Y84" t="n">
         <v>12</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="Z84" t="n">
         <v>25</v>
       </c>
-      <c r="AA83" t="n">
+      <c r="AA84" t="n">
         <v>70</v>
       </c>
-      <c r="AB83" t="n">
+      <c r="AB84" t="n">
         <v>11</v>
       </c>
-      <c r="AC83" t="n">
+      <c r="AC84" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD83" t="n">
+      <c r="AD84" t="n">
         <v>17</v>
       </c>
-      <c r="AE83" t="n">
+      <c r="AE84" t="n">
         <v>55</v>
       </c>
-      <c r="AF83" t="n">
+      <c r="AF84" t="n">
         <v>21</v>
       </c>
-      <c r="AG83" t="n">
+      <c r="AG84" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH83" t="n">
+      <c r="AH84" t="n">
         <v>25</v>
       </c>
-      <c r="AI83" t="n">
+      <c r="AI84" t="n">
         <v>75</v>
       </c>
-      <c r="AJ83" t="n">
+      <c r="AJ84" t="n">
         <v>55</v>
       </c>
-      <c r="AK83" t="n">
+      <c r="AK84" t="n">
         <v>44</v>
       </c>
-      <c r="AL83" t="n">
+      <c r="AL84" t="n">
         <v>70</v>
       </c>
-      <c r="AM83" t="n">
+      <c r="AM84" t="n">
         <v>170</v>
       </c>
-      <c r="AN83" t="n">
+      <c r="AN84" t="n">
         <v>46</v>
       </c>
-      <c r="AO83" t="n">
+      <c r="AO84" t="n">
         <v>60</v>
       </c>
-      <c r="AP83" t="n">
+      <c r="AP84" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ83" t="n">
+      <c r="AQ84" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR83" t="n">
+      <c r="AR84" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS83" t="n">
+      <c r="AS84" t="n">
         <v>4</v>
       </c>
-      <c r="AT83" t="n">
+      <c r="AT84" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU83" t="n">
+      <c r="AU84" t="n">
         <v>5.4</v>
       </c>
-      <c r="AV83" t="n">
+      <c r="AV84" t="n">
         <v>10</v>
       </c>
-      <c r="AW83" t="n">
+      <c r="AW84" t="n">
         <v>3.95</v>
       </c>
-      <c r="AX83" t="n">
+      <c r="AX84" t="n">
         <v>12</v>
       </c>
-      <c r="AY83" t="n">
+      <c r="AY84" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ83" t="n">
+      <c r="AZ84" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA83" t="n">
+      <c r="BA84" t="n">
         <v>4</v>
       </c>
-      <c r="BB83" t="n">
+      <c r="BB84" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC83" t="n">
+      <c r="BC84" t="n">
         <v>3.9</v>
       </c>
-      <c r="BD83" t="n">
+      <c r="BD84" t="n">
         <v>4</v>
       </c>
-      <c r="BE83" t="n">
+      <c r="BE84" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF83" t="n">
+      <c r="BF84" t="n">
         <v>3.9</v>
       </c>
-      <c r="BG83" t="n">
+      <c r="BG84" t="n">
         <v>4</v>
       </c>
-      <c r="BH83" t="n">
+      <c r="BH84" t="n">
         <v>3.05</v>
       </c>
-      <c r="BI83" t="n">
+      <c r="BI84" t="n">
         <v>2.38</v>
       </c>
-      <c r="BJ83" t="n">
+      <c r="BJ84" t="n">
         <v>11</v>
       </c>
-      <c r="BK83" t="n">
+      <c r="BK84" t="n">
         <v>5.2</v>
       </c>
-      <c r="BL83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM83" t="n">
+      <c r="BL84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM84" t="n">
         <v>2.3</v>
       </c>
-      <c r="BN83" t="n">
+      <c r="BN84" t="n">
         <v>5.7</v>
       </c>
-      <c r="BO83" t="n">
+      <c r="BO84" t="n">
         <v>3.6</v>
       </c>
-      <c r="BP83" t="n">
+      <c r="BP84" t="n">
         <v>24</v>
       </c>
-      <c r="BQ83" t="n">
+      <c r="BQ84" t="n">
         <v>7</v>
       </c>
-      <c r="BR83" t="n">
+      <c r="BR84" t="n">
         <v>44</v>
       </c>
-      <c r="BS83" t="n">
+      <c r="BS84" t="n">
         <v>2.22</v>
       </c>
-      <c r="BT83" t="n">
+      <c r="BT84" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU83" t="n">
+      <c r="BU84" t="n">
         <v>3.9</v>
       </c>
-      <c r="BV83" t="n">
+      <c r="BV84" t="n">
         <v>29</v>
       </c>
-      <c r="BW83" t="n">
+      <c r="BW84" t="n">
         <v>2.16</v>
       </c>
-      <c r="BX83" t="n">
+      <c r="BX84" t="n">
         <v>48</v>
       </c>
-      <c r="BY83" t="n">
+      <c r="BY84" t="n">
         <v>2.22</v>
       </c>
-      <c r="BZ83" t="n">
+      <c r="BZ84" t="n">
         <v>42</v>
       </c>
-      <c r="CA83" t="n">
+      <c r="CA84" t="n">
         <v>2.2</v>
       </c>
-      <c r="CB83" t="inlineStr">
-        <is>
-          <t>2026-05-29 17:24:24</t>
+      <c r="CB84" t="inlineStr">
+        <is>
+          <t>2026-05-29 19:49:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -863,7 +863,7 @@
         <v>1.39</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>16</v>
@@ -890,19 +890,19 @@
         <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
         <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
@@ -956,7 +956,7 @@
         <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AN2" t="n">
         <v>7.2</v>
@@ -968,7 +968,7 @@
         <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
         <v>4.6</v>
@@ -1028,19 +1028,19 @@
         <v>14.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.45</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BP2" t="n">
         <v>7.8</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
         <v>16</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1419,7 +1419,7 @@
         <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1470,16 +1470,16 @@
         <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="I5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1646,10 +1646,10 @@
         <v>2.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>1.86</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -2169,13 +2169,13 @@
         <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
         <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2292,19 +2292,19 @@
         <v>3.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,41 +2316,41 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU7" t="n">
         <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
         <v>5.7</v>
@@ -2414,13 +2414,13 @@
         <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2432,7 +2432,7 @@
         <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -2644,10 +2644,10 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
@@ -2683,7 +2683,7 @@
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
         <v>2.28</v>
@@ -2767,10 +2767,10 @@
         <v>4.8</v>
       </c>
       <c r="AX9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
         <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2922,7 +2922,7 @@
         <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
         <v>1.58</v>
@@ -2937,10 +2937,10 @@
         <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
         <v>29</v>
@@ -2997,7 +2997,7 @@
         <v>15.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10" t="n">
         <v>12</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
         <v>2.98</v>
@@ -3155,7 +3155,7 @@
         <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.7</v>
@@ -3173,49 +3173,49 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
         <v>9.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>44</v>
@@ -3224,7 +3224,7 @@
         <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
@@ -3260,7 +3260,7 @@
         <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -3272,7 +3272,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -3284,25 +3284,25 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.9</v>
+        <v>25</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
         <v>18.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J12" t="n">
         <v>3.85</v>
@@ -3421,16 +3421,16 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R12" t="n">
         <v>1.58</v>
@@ -3442,7 +3442,7 @@
         <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
         <v>1.83</v>
@@ -3457,16 +3457,16 @@
         <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
@@ -3478,7 +3478,7 @@
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>14.5</v>
@@ -3490,7 +3490,7 @@
         <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
         <v>40</v>
@@ -3502,28 +3502,28 @@
         <v>28</v>
       </c>
       <c r="AO12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
         <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
         <v>17.5</v>
@@ -3547,16 +3547,16 @@
         <v>30</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
         <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="n">
         <v>4.3</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
         <v>2.72</v>
@@ -3672,13 +3672,13 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
         <v>1.96</v>
@@ -3687,130 +3687,130 @@
         <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO13" t="n">
         <v>27</v>
       </c>
-      <c r="AA13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AP13" t="n">
         <v>11</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
         <v>16</v>
       </c>
-      <c r="AE13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF13" t="n">
         <v>18</v>
       </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2</v>
-      </c>
       <c r="BG13" t="n">
-        <v>2</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
         <v>1.17</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
         <v>2.9</v>
@@ -4691,10 +4691,10 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>2.22</v>
@@ -4703,13 +4703,13 @@
         <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
         <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
         <v>2.4</v>
@@ -4775,7 +4775,7 @@
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -4787,7 +4787,7 @@
         <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU17" t="n">
         <v>6.6</v>
@@ -4823,7 +4823,7 @@
         <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
         <v>16</v>
@@ -4856,10 +4856,10 @@
         <v>17</v>
       </c>
       <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS17" t="n">
         <v>9.800000000000001</v>
@@ -4874,7 +4874,7 @@
         <v>22</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX17" t="n">
         <v>30</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
         <v>1.25</v>
@@ -4960,7 +4960,7 @@
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>5.6</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -5196,13 +5196,13 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
         <v>2.02</v>
@@ -5211,16 +5211,16 @@
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
         <v>1.17</v>
@@ -5244,7 +5244,7 @@
         <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -5283,10 +5283,10 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
         <v>1.03</v>
@@ -5295,34 +5295,34 @@
         <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
         <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD19" t="n">
         <v>1.03</v>
@@ -5331,10 +5331,10 @@
         <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH19" t="n">
         <v>4.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
         <v>2.2</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5725,10 +5725,10 @@
         <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
         <v>1.16</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>2.54</v>
       </c>
       <c r="I22" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
         <v>3.6</v>
@@ -5958,10 +5958,10 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -5970,13 +5970,13 @@
         <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -5985,10 +5985,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W22" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -6723,10 +6723,10 @@
         <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P25" t="n">
         <v>1.67</v>
@@ -6741,10 +6741,10 @@
         <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>1.41</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -7485,19 +7485,19 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q28" t="n">
         <v>1.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
         <v>1.18</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
         <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
         <v>1.02</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -7993,10 +7993,10 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P30" t="n">
         <v>1.97</v>
@@ -8005,10 +8005,10 @@
         <v>1.86</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
         <v>1.78</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
         <v>2.12</v>
       </c>
       <c r="I31" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J31" t="n">
         <v>3.65</v>
@@ -8244,13 +8244,13 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P31" t="n">
         <v>2.18</v>
@@ -8259,130 +8259,130 @@
         <v>1.76</v>
       </c>
       <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.36</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X31" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z31" t="n">
         <v>16</v>
       </c>
-      <c r="Z31" t="n">
-        <v>21</v>
-      </c>
       <c r="AA31" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AB31" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AC31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR31" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AT31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
         <v>10</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -8501,19 +8501,19 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
         <v>1.11</v>
       </c>
       <c r="P32" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -9263,16 +9263,16 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O35" t="n">
         <v>1.13</v>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R35" t="n">
         <v>1.6</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
         <v>1.75</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
         <v>2.88</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -10022,10 +10022,10 @@
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O38" t="n">
         <v>1.17</v>
@@ -10043,10 +10043,10 @@
         <v>2.3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V38" t="n">
         <v>2</v>
@@ -10082,13 +10082,13 @@
         <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH38" t="n">
         <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -10142,7 +10142,7 @@
         <v>1.03</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB38" t="n">
         <v>1.03</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10279,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>2.5</v>
       </c>
       <c r="G40" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>2.72</v>
       </c>
       <c r="I40" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
@@ -10530,22 +10530,22 @@
         <v>1.01</v>
       </c>
       <c r="M40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N40" t="n">
         <v>2.32</v>
       </c>
       <c r="O40" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
         <v>1.74</v>
       </c>
       <c r="R40" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
         <v>2.4</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W40" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>1.56</v>
       </c>
       <c r="G41" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H41" t="n">
         <v>6.6</v>
@@ -10799,7 +10799,7 @@
         <v>2.02</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
         <v>3.7</v>
@@ -10832,7 +10832,7 @@
         <v>8.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD41" t="n">
         <v>34</v>
@@ -10874,37 +10874,37 @@
         <v>10</v>
       </c>
       <c r="AQ41" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT41" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV41" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB41" t="n">
         <v>11</v>
@@ -10913,16 +10913,16 @@
         <v>13.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH41" t="n">
         <v>3.4</v>
@@ -10946,7 +10946,7 @@
         <v>4.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP41" t="n">
         <v>11.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -11017,16 +11017,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G42" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
         <v>5.2</v>
@@ -11035,22 +11035,22 @@
         <v>5.4</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M42" t="n">
         <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P42" t="n">
         <v>2.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R42" t="n">
         <v>1.61</v>
@@ -11062,25 +11062,25 @@
         <v>1.84</v>
       </c>
       <c r="U42" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V42" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W42" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="X42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z42" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA42" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB42" t="n">
         <v>11</v>
@@ -11089,7 +11089,7 @@
         <v>13</v>
       </c>
       <c r="AD42" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE42" t="n">
         <v>140</v>
@@ -11098,13 +11098,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG42" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH42" t="n">
         <v>26</v>
       </c>
       <c r="AI42" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ42" t="n">
         <v>12</v>
@@ -11119,19 +11119,19 @@
         <v>140</v>
       </c>
       <c r="AN42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO42" t="n">
         <v>140</v>
       </c>
       <c r="AP42" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AQ42" t="n">
         <v>34</v>
       </c>
       <c r="AR42" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS42" t="n">
         <v>3.7</v>
@@ -11140,25 +11140,25 @@
         <v>9.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV42" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW42" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX42" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BB42" t="n">
         <v>9.6</v>
@@ -11167,22 +11167,22 @@
         <v>12.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG42" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -11274,10 +11274,10 @@
         <v>1.54</v>
       </c>
       <c r="G43" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H43" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I43" t="n">
         <v>8.199999999999999</v>
@@ -11322,7 +11322,7 @@
         <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X43" t="n">
         <v>15.5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -11531,13 +11531,13 @@
         <v>5.1</v>
       </c>
       <c r="H44" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I44" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J44" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K44" t="n">
         <v>3.6</v>
@@ -11549,37 +11549,37 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>1.39</v>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R44" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T44" t="n">
         <v>1.95</v>
       </c>
       <c r="U44" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V44" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W44" t="n">
         <v>1.24</v>
       </c>
       <c r="X44" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
         <v>9</v>
@@ -11618,7 +11618,7 @@
         <v>120</v>
       </c>
       <c r="AK44" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL44" t="n">
         <v>95</v>
@@ -11651,16 +11651,16 @@
         <v>7.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW44" t="n">
         <v>19</v>
       </c>
       <c r="AX44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY44" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ44" t="n">
         <v>18</v>
@@ -11669,22 +11669,22 @@
         <v>36</v>
       </c>
       <c r="BB44" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BD44" t="n">
         <v>55</v>
       </c>
       <c r="BE44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF44" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG44" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G45" t="n">
         <v>1.46</v>
@@ -11791,10 +11791,10 @@
         <v>8.4</v>
       </c>
       <c r="J45" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -11860,7 +11860,7 @@
         <v>11.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH45" t="n">
         <v>25</v>
@@ -11896,7 +11896,7 @@
         <v>8.4</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT45" t="n">
         <v>9.4</v>
@@ -11932,7 +11932,7 @@
         <v>25</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BF45" t="n">
         <v>5</v>
@@ -11941,7 +11941,7 @@
         <v>7</v>
       </c>
       <c r="BH45" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI45" t="n">
         <v>3.05</v>
@@ -11950,13 +11950,13 @@
         <v>15</v>
       </c>
       <c r="BK45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BN45" t="n">
         <v>5.9</v>
@@ -11974,35 +11974,35 @@
         <v>30</v>
       </c>
       <c r="BS45" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BT45" t="n">
         <v>16</v>
       </c>
       <c r="BU45" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BV45" t="n">
         <v>1000</v>
       </c>
       <c r="BW45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BX45" t="n">
         <v>1000</v>
       </c>
       <c r="BY45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BZ45" t="n">
         <v>17.5</v>
       </c>
       <c r="CA45" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -12042,7 +12042,7 @@
         <v>2.68</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J46" t="n">
         <v>3.45</v>
@@ -12057,16 +12057,16 @@
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O46" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P46" t="n">
         <v>1.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R46" t="n">
         <v>1.38</v>
@@ -12075,124 +12075,124 @@
         <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V46" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W46" t="n">
         <v>1.53</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
         <v>1.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -12290,16 +12290,16 @@
         <v>1.6</v>
       </c>
       <c r="G47" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H47" t="n">
         <v>5.5</v>
       </c>
       <c r="I47" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K47" t="n">
         <v>5.2</v>
@@ -12338,7 +12338,7 @@
         <v>1.2</v>
       </c>
       <c r="W47" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="X47" t="n">
         <v>30</v>
@@ -12404,7 +12404,7 @@
         <v>4.3</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT47" t="n">
         <v>10</v>
@@ -12440,7 +12440,7 @@
         <v>4.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF47" t="n">
         <v>5</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
         <v>3.75</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -12565,7 +12565,7 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="O48" t="n">
         <v>1.23</v>
@@ -12577,7 +12577,7 @@
         <v>1.74</v>
       </c>
       <c r="R48" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S48" t="n">
         <v>2.6</v>
@@ -12589,7 +12589,7 @@
         <v>2.24</v>
       </c>
       <c r="V48" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W48" t="n">
         <v>1.43</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H49" t="n">
         <v>2.18</v>
@@ -12807,10 +12807,10 @@
         <v>2.22</v>
       </c>
       <c r="J49" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L49" t="n">
         <v>1.33</v>
@@ -12819,7 +12819,7 @@
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>1.37</v>
@@ -12831,7 +12831,7 @@
         <v>2.14</v>
       </c>
       <c r="R49" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -12846,7 +12846,7 @@
         <v>1.81</v>
       </c>
       <c r="W49" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X49" t="n">
         <v>13</v>
@@ -12870,13 +12870,13 @@
         <v>11.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF49" t="n">
         <v>25</v>
       </c>
       <c r="AG49" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH49" t="n">
         <v>21</v>
@@ -12888,7 +12888,7 @@
         <v>75</v>
       </c>
       <c r="AK49" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL49" t="n">
         <v>65</v>
@@ -12897,7 +12897,7 @@
         <v>120</v>
       </c>
       <c r="AN49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO49" t="n">
         <v>22</v>
@@ -12912,7 +12912,7 @@
         <v>11.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT49" t="n">
         <v>11</v>
@@ -12924,7 +12924,7 @@
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX49" t="n">
         <v>22</v>
@@ -12939,7 +12939,7 @@
         <v>38</v>
       </c>
       <c r="BB49" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC49" t="n">
         <v>40</v>
@@ -12948,10 +12948,10 @@
         <v>50</v>
       </c>
       <c r="BE49" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF49" t="n">
         <v>10</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BG49" t="n">
         <v>18</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
         <v>1.24</v>
       </c>
       <c r="S51" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O52" t="n">
         <v>1.18</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13844,7 @@
         <v>1.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R53" t="n">
         <v>1.12</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         <v>1.08</v>
       </c>
       <c r="N55" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="O55" t="n">
         <v>1.38</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
         <v>2.66</v>
       </c>
       <c r="G56" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H56" t="n">
         <v>2.74</v>
@@ -14585,148 +14585,148 @@
         <v>3.1</v>
       </c>
       <c r="J56" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K56" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N56" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S56" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="T56" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U56" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="V56" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W56" t="n">
         <v>1.51</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z56" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB56" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC56" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD56" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE56" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF56" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG56" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH56" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK56" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AV56" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
         <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14836,7 @@
         <v>1.76</v>
       </c>
       <c r="I57" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J57" t="n">
         <v>3.4</v>
@@ -14878,10 +14878,10 @@
         <v>2.12</v>
       </c>
       <c r="W57" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X57" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
         <v>7.6</v>
@@ -14893,10 +14893,10 @@
         <v>22</v>
       </c>
       <c r="AB57" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD57" t="n">
         <v>12</v>
@@ -14905,19 +14905,19 @@
         <v>25</v>
       </c>
       <c r="AF57" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH57" t="n">
         <v>27</v>
       </c>
       <c r="AI57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ57" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK57" t="n">
         <v>110</v>
@@ -14929,7 +14929,7 @@
         <v>190</v>
       </c>
       <c r="AN57" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO57" t="n">
         <v>17</v>
@@ -14947,7 +14947,7 @@
         <v>15</v>
       </c>
       <c r="AT57" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU57" t="n">
         <v>6.4</v>
@@ -14959,31 +14959,31 @@
         <v>16.5</v>
       </c>
       <c r="AX57" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AY57" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB57" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC57" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD57" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE57" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF57" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG57" t="n">
         <v>11.5</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O59" t="n">
         <v>1.01</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -15592,10 +15592,10 @@
         <v>1.6</v>
       </c>
       <c r="G60" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H60" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I60" t="n">
         <v>6.8</v>
@@ -15604,7 +15604,7 @@
         <v>3.55</v>
       </c>
       <c r="K60" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -15622,7 +15622,7 @@
         <v>2.08</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R60" t="n">
         <v>1.44</v>
@@ -15640,7 +15640,7 @@
         <v>1.17</v>
       </c>
       <c r="W60" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -15843,16 +15843,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G61" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H61" t="n">
         <v>2.4</v>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>3.25</v>
@@ -15891,7 +15891,7 @@
         <v>2.12</v>
       </c>
       <c r="V61" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W61" t="n">
         <v>1.43</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
         <v>2.1</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H62" t="n">
         <v>3.4</v>
@@ -16109,7 +16109,7 @@
         <v>3.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K62" t="n">
         <v>3.85</v>
@@ -16148,7 +16148,7 @@
         <v>1.34</v>
       </c>
       <c r="W62" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X62" t="n">
         <v>970</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -16351,61 +16351,61 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G63" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H63" t="n">
         <v>5.5</v>
       </c>
       <c r="I63" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K63" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M63" t="n">
         <v>1.06</v>
       </c>
       <c r="N63" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
         <v>1.29</v>
       </c>
       <c r="P63" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R63" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S63" t="n">
         <v>3.2</v>
       </c>
       <c r="T63" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U63" t="n">
         <v>2.16</v>
       </c>
       <c r="V63" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W63" t="n">
         <v>2.2</v>
       </c>
       <c r="X63" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y63" t="n">
         <v>21</v>
@@ -16417,7 +16417,7 @@
         <v>140</v>
       </c>
       <c r="AB63" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC63" t="n">
         <v>8.4</v>
@@ -16438,7 +16438,7 @@
         <v>19</v>
       </c>
       <c r="AI63" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ63" t="n">
         <v>20</v>
@@ -16456,34 +16456,34 @@
         <v>12</v>
       </c>
       <c r="AO63" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ63" t="n">
         <v>19.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>9.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS63" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AT63" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU63" t="n">
         <v>7.4</v>
       </c>
       <c r="AV63" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="AW63" t="n">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="AX63" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY63" t="n">
         <v>9.4</v>
@@ -16492,89 +16492,89 @@
         <v>17</v>
       </c>
       <c r="BA63" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB63" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="BC63" t="n">
         <v>17.5</v>
       </c>
       <c r="BD63" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BE63" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BF63" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG63" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BH63" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ63" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.68</v>
+        <v>5.1</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.92</v>
+        <v>9.6</v>
       </c>
       <c r="BN63" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO63" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP63" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.74</v>
+        <v>5.8</v>
       </c>
       <c r="BR63" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.83</v>
+        <v>7.4</v>
       </c>
       <c r="BT63" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BU63" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV63" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX63" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.87</v>
+        <v>8.4</v>
       </c>
       <c r="BZ63" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.81</v>
+        <v>7</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -16605,22 +16605,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G64" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H64" t="n">
         <v>4.6</v>
       </c>
       <c r="I64" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J64" t="n">
         <v>3.1</v>
       </c>
       <c r="K64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L64" t="n">
         <v>1.43</v>
@@ -16653,16 +16653,16 @@
         <v>1.74</v>
       </c>
       <c r="V64" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W64" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X64" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z64" t="n">
         <v>42</v>
@@ -16719,22 +16719,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR64" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT64" t="n">
         <v>5.3</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV64" t="n">
         <v>15.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX64" t="n">
         <v>8.4</v>
@@ -16746,7 +16746,7 @@
         <v>18.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB64" t="n">
         <v>19</v>
@@ -16755,16 +16755,16 @@
         <v>20</v>
       </c>
       <c r="BD64" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE64" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF64" t="n">
         <v>18</v>
       </c>
       <c r="BG64" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -16871,7 +16871,7 @@
         <v>5</v>
       </c>
       <c r="J65" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K65" t="n">
         <v>3.5</v>
@@ -16886,7 +16886,7 @@
         <v>1.59</v>
       </c>
       <c r="O65" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P65" t="n">
         <v>1.59</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -17113,22 +17113,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G66" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H66" t="n">
         <v>12</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J66" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K66" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17146,7 +17146,7 @@
         <v>2.34</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17370,7 @@
         <v>2.12</v>
       </c>
       <c r="G67" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H67" t="n">
         <v>3.6</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
         <v>1.82</v>
       </c>
       <c r="G68" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H68" t="n">
         <v>5.1</v>
@@ -17633,10 +17633,10 @@
         <v>6.8</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K68" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -17672,7 +17672,7 @@
         <v>1.17</v>
       </c>
       <c r="W68" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X68" t="n">
         <v>9.800000000000001</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="AK68" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL68" t="n">
         <v>75</v>
@@ -17735,10 +17735,10 @@
         <v>10</v>
       </c>
       <c r="AR68" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT68" t="n">
         <v>4.8</v>
@@ -17750,7 +17750,7 @@
         <v>18</v>
       </c>
       <c r="AW68" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX68" t="n">
         <v>7.8</v>
@@ -17774,13 +17774,13 @@
         <v>4.9</v>
       </c>
       <c r="BE68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF68" t="n">
         <v>18</v>
       </c>
       <c r="BG68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH68" t="n">
         <v>2.78</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -18129,31 +18129,31 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G70" t="n">
         <v>2.38</v>
       </c>
       <c r="H70" t="n">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="I70" t="n">
         <v>3.4</v>
       </c>
       <c r="J70" t="n">
-        <v>3.3</v>
+        <v>1.45</v>
       </c>
       <c r="K70" t="n">
         <v>950</v>
       </c>
       <c r="L70" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M70" t="n">
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O70" t="n">
         <v>1.15</v>
@@ -18162,13 +18162,13 @@
         <v>1.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R70" t="n">
         <v>1.18</v>
       </c>
       <c r="S70" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="T70" t="n">
         <v>1.01</v>
@@ -18177,10 +18177,10 @@
         <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W70" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
         <v>5.9</v>
       </c>
       <c r="J72" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K72" t="n">
         <v>4.3</v>
@@ -18661,16 +18661,16 @@
         <v>1.06</v>
       </c>
       <c r="N72" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O72" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P72" t="n">
         <v>1.92</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R72" t="n">
         <v>1.35</v>
@@ -18757,7 +18757,7 @@
         <v>4.1</v>
       </c>
       <c r="AT72" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU72" t="n">
         <v>6.6</v>
@@ -18769,7 +18769,7 @@
         <v>4</v>
       </c>
       <c r="AX72" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY72" t="n">
         <v>7.4</v>
@@ -18793,7 +18793,7 @@
         <v>4.1</v>
       </c>
       <c r="BF72" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG72" t="n">
         <v>4.1</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
         <v>1.67</v>
       </c>
       <c r="I73" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="J73" t="n">
         <v>3.45</v>
@@ -18915,13 +18915,13 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O73" t="n">
         <v>1.37</v>
       </c>
       <c r="P73" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q73" t="n">
         <v>2.12</v>
@@ -18939,7 +18939,7 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W73" t="n">
         <v>1.16</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -19145,34 +19145,34 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G74" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="H74" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="K74" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="L74" t="n">
         <v>1.01</v>
       </c>
       <c r="M74" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N74" t="n">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="O74" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P74" t="n">
         <v>1.96</v>
@@ -19181,28 +19181,28 @@
         <v>1.84</v>
       </c>
       <c r="R74" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S74" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T74" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="U74" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V74" t="n">
         <v>1.06</v>
       </c>
       <c r="W74" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="X74" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y74" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z74" t="n">
         <v>1000</v>
@@ -19211,55 +19211,55 @@
         <v>1000</v>
       </c>
       <c r="AB74" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AC74" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD74" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE74" t="n">
         <v>1000</v>
       </c>
       <c r="AF74" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AG74" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH74" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI74" t="n">
         <v>1000</v>
       </c>
       <c r="AJ74" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AK74" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL74" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM74" t="n">
         <v>1000</v>
       </c>
       <c r="AN74" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO74" t="n">
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS74" t="n">
         <v>1.03</v>
@@ -19271,7 +19271,7 @@
         <v>1.01</v>
       </c>
       <c r="AV74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW74" t="n">
         <v>1.03</v>
@@ -19283,7 +19283,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA74" t="n">
         <v>1.03</v>
@@ -19295,7 +19295,7 @@
         <v>1.01</v>
       </c>
       <c r="BD74" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE74" t="n">
         <v>1.03</v>
@@ -19316,49 +19316,49 @@
         <v>1000</v>
       </c>
       <c r="BK74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL74" t="n">
         <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN74" t="n">
         <v>1000</v>
       </c>
       <c r="BO74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP74" t="n">
         <v>1000</v>
       </c>
       <c r="BQ74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR74" t="n">
         <v>1000</v>
       </c>
       <c r="BS74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT74" t="n">
         <v>1000</v>
       </c>
       <c r="BU74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV74" t="n">
         <v>1000</v>
       </c>
       <c r="BW74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX74" t="n">
         <v>1000</v>
       </c>
       <c r="BY74" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ74" t="n">
         <v>0</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19420,7 @@
         <v>1.01</v>
       </c>
       <c r="M75" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N75" t="n">
         <v>1.48</v>
@@ -19435,10 +19435,10 @@
         <v>1.89</v>
       </c>
       <c r="R75" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S75" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T75" t="n">
         <v>1.64</v>
@@ -19453,10 +19453,10 @@
         <v>1.42</v>
       </c>
       <c r="X75" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y75" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z75" t="n">
         <v>26</v>
@@ -19471,7 +19471,7 @@
         <v>10</v>
       </c>
       <c r="AD75" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE75" t="n">
         <v>1000</v>
@@ -19480,7 +19480,7 @@
         <v>26</v>
       </c>
       <c r="AG75" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH75" t="n">
         <v>26</v>
@@ -19507,7 +19507,7 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.01</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
         <v>1.93</v>
       </c>
       <c r="G76" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H76" t="n">
         <v>4.1</v>
@@ -19671,7 +19671,7 @@
         <v>3.9</v>
       </c>
       <c r="L76" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M76" t="n">
         <v>1.08</v>
@@ -19704,113 +19704,113 @@
         <v>1.25</v>
       </c>
       <c r="W76" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X76" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y76" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB76" t="n">
         <v>19.5</v>
       </c>
-      <c r="Z76" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ76" t="n">
+      <c r="BC76" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD76" t="n">
         <v>30</v>
       </c>
-      <c r="AK76" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV76" t="n">
+      <c r="BE76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF76" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY76" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ76" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB76" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC76" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE76" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF76" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG76" t="n">
         <v>1.01</v>
       </c>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -19907,22 +19907,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="G77" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H77" t="n">
         <v>2.18</v>
       </c>
       <c r="I77" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="J77" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K77" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -19943,10 +19943,10 @@
         <v>1.89</v>
       </c>
       <c r="R77" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S77" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T77" t="n">
         <v>1.7</v>
@@ -19955,10 +19955,10 @@
         <v>1.98</v>
       </c>
       <c r="V77" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W77" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X77" t="n">
         <v>1000</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -20173,7 +20173,7 @@
         <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K78" t="n">
         <v>950</v>
@@ -20185,7 +20185,7 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O78" t="n">
         <v>1.01</v>
@@ -20194,13 +20194,13 @@
         <v>1.24</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R78" t="n">
         <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -20669,7 +20669,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G80" t="n">
         <v>3.4</v>
@@ -20678,7 +20678,7 @@
         <v>2.62</v>
       </c>
       <c r="I80" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J80" t="n">
         <v>3.1</v>
@@ -20687,16 +20687,16 @@
         <v>3.55</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P80" t="n">
         <v>1.72</v>
@@ -20705,194 +20705,194 @@
         <v>2.16</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BN80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BO80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP80" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BR80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BT80" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV80" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BW80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BX80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BZ80" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="CA80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -20941,16 +20941,16 @@
         <v>3.6</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P81" t="n">
         <v>1.76</v>
@@ -20959,194 +20959,194 @@
         <v>2.12</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -21449,16 +21449,16 @@
         <v>3.25</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P83" t="n">
         <v>1.46</v>
@@ -21467,194 +21467,194 @@
         <v>2.74</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BG83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BH83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G84" t="n">
         <v>2.92</v>
@@ -21727,13 +21727,13 @@
         <v>4.4</v>
       </c>
       <c r="T84" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U84" t="n">
         <v>1.88</v>
       </c>
       <c r="V84" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W84" t="n">
         <v>1.52</v>
@@ -21820,7 +21820,7 @@
         <v>12</v>
       </c>
       <c r="AY84" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ84" t="n">
         <v>14.5</v>
@@ -21856,7 +21856,7 @@
         <v>11</v>
       </c>
       <c r="BK84" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL84" t="n">
         <v>1000</v>
@@ -21865,7 +21865,7 @@
         <v>2.3</v>
       </c>
       <c r="BN84" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO84" t="n">
         <v>3.6</v>
@@ -21874,25 +21874,25 @@
         <v>24</v>
       </c>
       <c r="BQ84" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR84" t="n">
         <v>44</v>
       </c>
       <c r="BS84" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BT84" t="n">
         <v>6.4</v>
       </c>
       <c r="BU84" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV84" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW84" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BX84" t="n">
         <v>48</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-29 19:49:09</t>
+          <t>2026-05-29 22:15:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB84"/>
+  <dimension ref="A1:CB86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="H2" t="n">
         <v>8.800000000000001</v>
@@ -893,7 +893,7 @@
         <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
         <v>2.74</v>
@@ -914,7 +914,7 @@
         <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="n">
         <v>180</v>
@@ -923,31 +923,31 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
         <v>65</v>
       </c>
       <c r="AE2" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="n">
         <v>310</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>21</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BC2" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1407,10 +1407,10 @@
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
         <v>1.83</v>
@@ -1419,7 +1419,7 @@
         <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1470,16 +1470,16 @@
         <v>60</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
         <v>19.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>4.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
         <v>1.75</v>
       </c>
       <c r="I5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
@@ -1640,37 +1640,37 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
         <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1688,19 +1688,19 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>44</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>23</v>
@@ -1733,49 +1733,49 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
         <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
         <v>9.199999999999999</v>
@@ -1784,7 +1784,7 @@
         <v>6.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.37</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.37</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.37</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.37</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.37</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -2136,13 +2136,13 @@
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -2163,19 +2163,19 @@
         <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
         <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2256,10 +2256,10 @@
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
@@ -2283,7 +2283,7 @@
         <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
         <v>19</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -2644,10 +2644,10 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
@@ -2680,7 +2680,7 @@
         <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
         <v>1.19</v>
@@ -2770,7 +2770,7 @@
         <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2922,22 +2922,22 @@
         <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
         <v>1.51</v>
@@ -3012,7 +3012,7 @@
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -3024,7 +3024,7 @@
         <v>17.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
@@ -3048,7 +3048,7 @@
         <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="n">
         <v>4.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.37</v>
@@ -3173,10 +3173,10 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
@@ -3185,16 +3185,16 @@
         <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X11" t="n">
         <v>15.5</v>
@@ -3260,7 +3260,7 @@
         <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
         <v>8.800000000000001</v>
@@ -3269,13 +3269,13 @@
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
@@ -3284,7 +3284,7 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
@@ -3293,7 +3293,7 @@
         <v>25</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
         <v>4.8</v>
@@ -3302,7 +3302,7 @@
         <v>18.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
         <v>3.65</v>
@@ -3406,7 +3406,7 @@
         <v>2.14</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.85</v>
@@ -3421,34 +3421,34 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>1.63</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
         <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V12" t="n">
         <v>1.83</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3484,13 +3484,13 @@
         <v>14.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
         <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>40</v>
@@ -3499,7 +3499,7 @@
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO12" t="n">
         <v>11.5</v>
@@ -3511,16 +3511,16 @@
         <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -3654,10 +3654,10 @@
         <v>2.68</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
         <v>2.86</v>
@@ -3675,19 +3675,19 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
@@ -3720,7 +3720,7 @@
         <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
@@ -3759,52 +3759,52 @@
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
         <v>16</v>
       </c>
       <c r="AS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
         <v>7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>2.28</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I17" t="n">
         <v>3.2</v>
@@ -4694,7 +4694,7 @@
         <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
         <v>2.22</v>
@@ -4706,7 +4706,7 @@
         <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
         <v>1.61</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="n">
         <v>5.6</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5202,85 +5202,85 @@
         <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.98</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP19" t="n">
         <v>13</v>
@@ -5289,13 +5289,13 @@
         <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
         <v>7.4</v>
@@ -5304,7 +5304,7 @@
         <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX19" t="n">
         <v>8</v>
@@ -5316,7 +5316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -5325,80 +5325,80 @@
         <v>13</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.29</v>
+        <v>9.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.29</v>
+        <v>5.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.29</v>
+        <v>8.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.29</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.29</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -5845,58 +5845,58 @@
         <v>4.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -6197,16 +6197,16 @@
         <v>3.15</v>
       </c>
       <c r="H23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I23" t="n">
         <v>2.52</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6233,7 +6233,7 @@
         <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U23" t="n">
         <v>2.28</v>
@@ -6242,7 +6242,7 @@
         <v>1.66</v>
       </c>
       <c r="W23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
         <v>28</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
         <v>2.3</v>
@@ -6454,13 +6454,13 @@
         <v>3.65</v>
       </c>
       <c r="I24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
         <v>2.14</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
         <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6741,10 +6741,10 @@
         <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V25" t="n">
         <v>1.41</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -7207,28 +7207,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N27" t="n">
         <v>2.28</v>
@@ -7240,7 +7240,7 @@
         <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R27" t="n">
         <v>1.42</v>
@@ -7255,16 +7255,16 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -7279,7 +7279,7 @@
         <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
@@ -7291,7 +7291,7 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -7300,16 +7300,16 @@
         <v>970</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -7327,22 +7327,22 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ27" t="n">
         <v>1.01</v>
@@ -7351,10 +7351,10 @@
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BD27" t="n">
         <v>1.01</v>
@@ -7363,7 +7363,7 @@
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         <v>1.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
         <v>1.18</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K29" t="n">
         <v>3.95</v>
@@ -7766,7 +7766,7 @@
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G30" t="n">
         <v>1.88</v>
@@ -7978,13 +7978,13 @@
         <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -7993,43 +7993,43 @@
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
         <v>1.28</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R30" t="n">
         <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U30" t="n">
         <v>2.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
         <v>2.12</v>
       </c>
       <c r="X30" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AA30" t="n">
         <v>140</v>
@@ -8038,97 +8038,97 @@
         <v>9.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI30" t="n">
         <v>85</v>
       </c>
       <c r="AJ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK30" t="n">
         <v>24</v>
       </c>
-      <c r="AK30" t="n">
-        <v>22</v>
-      </c>
       <c r="AL30" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="n">
         <v>110</v>
       </c>
       <c r="AN30" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>15</v>
       </c>
-      <c r="AR30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV30" t="n">
+      <c r="BA30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC30" t="n">
         <v>16</v>
       </c>
-      <c r="AW30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BF30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
         <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
         <v>1.03</v>
@@ -8388,40 +8388,40 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BJ31" t="n">
         <v>12.5</v>
       </c>
       <c r="BK31" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BN31" t="n">
         <v>9.4</v>
       </c>
       <c r="BO31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BR31" t="n">
         <v>48</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BT31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU31" t="n">
         <v>3.55</v>
@@ -8436,17 +8436,17 @@
         <v>36</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BZ31" t="n">
         <v>29</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -8480,13 +8480,13 @@
         <v>2.84</v>
       </c>
       <c r="G32" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H32" t="n">
         <v>2.18</v>
       </c>
       <c r="I32" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
@@ -8498,145 +8498,145 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N32" t="n">
         <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P32" t="n">
         <v>2.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R32" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W32" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP32" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
         <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G33" t="n">
         <v>3.1</v>
@@ -8755,13 +8755,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
         <v>1.48</v>
@@ -8779,7 +8779,7 @@
         <v>2.62</v>
       </c>
       <c r="V33" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W33" t="n">
         <v>1.47</v>
@@ -8836,10 +8836,10 @@
         <v>15.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>13</v>
@@ -8848,7 +8848,7 @@
         <v>15.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
         <v>14.5</v>
@@ -8872,19 +8872,19 @@
         <v>12.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD33" t="n">
         <v>5.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF33" t="n">
         <v>11.5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
         <v>1.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S34" t="n">
         <v>1.87</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G35" t="n">
         <v>2.04</v>
@@ -9257,212 +9257,212 @@
         <v>4.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.76</v>
+        <v>5.7</v>
       </c>
       <c r="O35" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R35" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="S35" t="n">
         <v>2.12</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V35" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
         <v>1.96</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP35" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AR35" t="n">
         <v>1.03</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
         <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q36" t="n">
         <v>1.73</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>1.62</v>
       </c>
       <c r="G37" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H37" t="n">
         <v>5.3</v>
@@ -9780,7 +9780,7 @@
         <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R37" t="n">
         <v>1.37</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
         <v>1.84</v>
       </c>
       <c r="I38" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -10019,212 +10019,212 @@
         <v>4.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M38" t="n">
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P38" t="n">
         <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R38" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T38" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="U38" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W38" t="n">
         <v>1.28</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX38" t="n">
         <v>22</v>
       </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX38" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -10512,16 +10512,16 @@
         <v>2.5</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="H40" t="n">
         <v>2.72</v>
       </c>
       <c r="I40" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J40" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K40" t="n">
         <v>4</v>
@@ -10539,10 +10539,10 @@
         <v>1.21</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="R40" t="n">
         <v>1.39</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
         <v>4.1</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP41" t="n">
         <v>11.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -11149,10 +11149,10 @@
         <v>16.5</v>
       </c>
       <c r="AX42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
         <v>19.5</v>
@@ -11161,7 +11161,7 @@
         <v>16</v>
       </c>
       <c r="BB42" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC42" t="n">
         <v>12.5</v>
@@ -11176,13 +11176,13 @@
         <v>4.7</v>
       </c>
       <c r="BG42" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11197,13 +11197,13 @@
         <v>1.01</v>
       </c>
       <c r="BN42" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP42" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ42" t="n">
         <v>1.01</v>
@@ -11215,7 +11215,7 @@
         <v>1.01</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU42" t="n">
         <v>1.01</v>
@@ -11233,14 +11233,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ42" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA42" t="n">
         <v>1.01</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11307,7 @@
         <v>1.96</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S43" t="n">
         <v>3.4</v>
@@ -11322,7 +11322,7 @@
         <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X43" t="n">
         <v>15.5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>1.94</v>
       </c>
       <c r="J44" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
         <v>3.6</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>8.4</v>
       </c>
       <c r="J45" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K45" t="n">
         <v>5.6</v>
@@ -12002,14 +12002,14 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12024,175 +12024,175 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W46" t="n">
         <v>2.62</v>
       </c>
-      <c r="G46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.53</v>
-      </c>
       <c r="X46" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV46" t="n">
         <v>19</v>
       </c>
-      <c r="Y46" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP46" t="n">
+      <c r="AW46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC46" t="n">
         <v>11</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>21</v>
-      </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF46" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="BG46" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -12278,246 +12278,246 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.6</v>
+        <v>3.55</v>
       </c>
       <c r="G47" t="n">
-        <v>1.61</v>
+        <v>3.7</v>
       </c>
       <c r="H47" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="J47" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X47" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK47" t="n">
         <v>5.2</v>
       </c>
-      <c r="L47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N47" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W47" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X47" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN47" t="n">
+      <c r="BL47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ47" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO47" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW47" t="n">
+      <c r="BR47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU47" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT47" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV47" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW47" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX47" t="n">
         <v>1000</v>
       </c>
       <c r="BY47" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ47" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA47" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12532,175 +12532,175 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="G48" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="H48" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="I48" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="J48" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K48" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="O48" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R48" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U48" t="n">
         <v>2.24</v>
       </c>
       <c r="V48" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W48" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="X48" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Y48" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z48" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA48" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB48" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AC48" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD48" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF48" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK48" t="n">
         <v>30</v>
       </c>
-      <c r="AG48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>44</v>
-      </c>
       <c r="AL48" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM48" t="n">
         <v>100</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO48" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="AQ48" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.48</v>
+        <v>21</v>
       </c>
       <c r="AX48" t="n">
-        <v>2.48</v>
+        <v>13.5</v>
       </c>
       <c r="AY48" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.38</v>
+        <v>12</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BB48" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.54</v>
+        <v>21</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.62</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.7</v>
+        <v>17</v>
       </c>
       <c r="BG48" t="n">
-        <v>2.7</v>
+        <v>17.5</v>
       </c>
       <c r="BH48" t="n">
         <v>1000</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,239 +12786,239 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="G49" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="H49" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="I49" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="J49" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K49" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R49" t="n">
         <v>1.37</v>
       </c>
-      <c r="P49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="W49" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="X49" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Z49" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AA49" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE49" t="n">
         <v>32</v>
       </c>
-      <c r="AB49" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>26</v>
-      </c>
       <c r="AF49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG49" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH49" t="n">
         <v>21</v>
       </c>
       <c r="AI49" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK49" t="n">
         <v>44</v>
       </c>
-      <c r="AJ49" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>50</v>
       </c>
-      <c r="AL49" t="n">
-        <v>65</v>
-      </c>
       <c r="AM49" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN49" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>11</v>
+        <v>2.42</v>
       </c>
       <c r="AQ49" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="AR49" t="n">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="AS49" t="n">
-        <v>9</v>
+        <v>2.54</v>
       </c>
       <c r="AT49" t="n">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="AU49" t="n">
-        <v>7.2</v>
+        <v>2.18</v>
       </c>
       <c r="AV49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AY49" t="n">
         <v>10</v>
       </c>
-      <c r="AW49" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ49" t="n">
-        <v>18</v>
+        <v>2.38</v>
       </c>
       <c r="BA49" t="n">
-        <v>38</v>
+        <v>2.54</v>
       </c>
       <c r="BB49" t="n">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="BC49" t="n">
-        <v>40</v>
+        <v>2.54</v>
       </c>
       <c r="BD49" t="n">
-        <v>50</v>
+        <v>2.56</v>
       </c>
       <c r="BE49" t="n">
-        <v>11</v>
+        <v>2.62</v>
       </c>
       <c r="BF49" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="BG49" t="n">
-        <v>18</v>
+        <v>2.7</v>
       </c>
       <c r="BH49" t="n">
         <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BJ49" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="BN49" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO49" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP49" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BT49" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU49" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV49" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BX49" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BZ49" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14343,7 @@
         <v>1.08</v>
       </c>
       <c r="N55" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="O55" t="n">
         <v>1.38</v>
@@ -14391,7 +14391,7 @@
         <v>9.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE55" t="n">
         <v>1000</v>
@@ -14403,7 +14403,7 @@
         <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -14738,65 +14738,65 @@
         <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BJ56" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK56" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BL56" t="n">
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BN56" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO56" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP56" t="n">
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BT56" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU56" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV56" t="n">
         <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14830,7 @@
         <v>5.1</v>
       </c>
       <c r="G57" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H57" t="n">
         <v>1.76</v>
@@ -14878,7 +14878,7 @@
         <v>2.12</v>
       </c>
       <c r="W57" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X57" t="n">
         <v>13</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
         <v>1.12</v>
       </c>
       <c r="S58" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="T58" t="n">
         <v>1.01</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,239 +15834,239 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="G61" t="n">
-        <v>3.35</v>
+        <v>1.81</v>
       </c>
       <c r="H61" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K61" t="n">
         <v>3.7</v>
       </c>
       <c r="L61" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M61" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N61" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P61" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R61" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T61" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U61" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V61" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="W61" t="n">
-        <v>1.43</v>
+        <v>2.24</v>
       </c>
       <c r="X61" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ61" t="n">
         <v>17</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="BA61" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP61" t="n">
         <v>13</v>
       </c>
-      <c r="Z61" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA61" t="n">
+      <c r="BQ61" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR61" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV61" t="n">
         <v>40</v>
       </c>
-      <c r="AB61" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI61" t="n">
+      <c r="BW61" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX61" t="n">
         <v>46</v>
       </c>
-      <c r="AJ61" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU61" t="n">
+      <c r="BY61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ61" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA61" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV61" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ61" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA61" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -16320,14 +16320,14 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16342,184 +16342,184 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="G63" t="n">
-        <v>1.82</v>
+        <v>3.35</v>
       </c>
       <c r="H63" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="K63" t="n">
         <v>3.7</v>
       </c>
       <c r="L63" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O63" t="n">
         <v>1.3</v>
       </c>
-      <c r="M63" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.29</v>
-      </c>
       <c r="P63" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R63" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S63" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T63" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U63" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V63" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="W63" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="X63" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y63" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Z63" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="AA63" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="AB63" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AC63" t="n">
         <v>8.4</v>
       </c>
       <c r="AD63" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AE63" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AF63" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR63" t="n">
         <v>12</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AS63" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT63" t="n">
         <v>9.6</v>
       </c>
-      <c r="AH63" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AU63" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV63" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW63" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX63" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AY63" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ63" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BA63" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB63" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC63" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD63" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE63" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF63" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG63" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="BH63" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BI63" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="BJ63" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK63" t="n">
         <v>5.1</v>
@@ -16528,53 +16528,53 @@
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN63" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO63" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BP63" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="BQ63" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR63" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BS63" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT63" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BV63" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="BW63" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BX63" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BY63" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ63" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="CA63" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16955,7 @@
         <v>36</v>
       </c>
       <c r="AL65" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM65" t="n">
         <v>1000</v>
@@ -16976,7 +16976,7 @@
         <v>21</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AT65" t="n">
         <v>2.2</v>
@@ -16988,7 +16988,7 @@
         <v>14</v>
       </c>
       <c r="AW65" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AX65" t="n">
         <v>2.42</v>
@@ -17000,7 +17000,7 @@
         <v>2.62</v>
       </c>
       <c r="BA65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BB65" t="n">
         <v>19</v>
@@ -17012,13 +17012,13 @@
         <v>2.76</v>
       </c>
       <c r="BE65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BF65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BG65" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BH65" t="n">
         <v>1000</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17370,7 @@
         <v>2.12</v>
       </c>
       <c r="G67" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H67" t="n">
         <v>3.6</v>
@@ -17400,7 +17400,7 @@
         <v>1.83</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -17630,7 +17630,7 @@
         <v>5.1</v>
       </c>
       <c r="I68" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>3.05</v>
@@ -17639,28 +17639,28 @@
         <v>3.6</v>
       </c>
       <c r="L68" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M68" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N68" t="n">
-        <v>1.38</v>
+        <v>2.46</v>
       </c>
       <c r="O68" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="P68" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R68" t="n">
         <v>1.17</v>
       </c>
       <c r="S68" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="T68" t="n">
         <v>2.24</v>
@@ -17669,7 +17669,7 @@
         <v>1.64</v>
       </c>
       <c r="V68" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W68" t="n">
         <v>1.96</v>
@@ -17786,7 +17786,7 @@
         <v>2.78</v>
       </c>
       <c r="BI68" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BJ68" t="n">
         <v>13</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -18129,13 +18129,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G70" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H70" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="I70" t="n">
         <v>3.4</v>
@@ -18144,7 +18144,7 @@
         <v>1.45</v>
       </c>
       <c r="K70" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -18177,10 +18177,10 @@
         <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W70" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -18413,16 +18413,16 @@
         <v>1.01</v>
       </c>
       <c r="P71" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R71" t="n">
         <v>1.18</v>
       </c>
       <c r="S71" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T71" t="n">
         <v>1.01</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18769,7 @@
         <v>4</v>
       </c>
       <c r="AX72" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY72" t="n">
         <v>7.4</v>
@@ -18793,7 +18793,7 @@
         <v>4.1</v>
       </c>
       <c r="BF72" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG72" t="n">
         <v>4.1</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
         <v>1.67</v>
       </c>
       <c r="I73" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J73" t="n">
         <v>3.45</v>
@@ -18927,10 +18927,10 @@
         <v>2.12</v>
       </c>
       <c r="R73" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S73" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="T73" t="n">
         <v>1.01</v>
@@ -18939,7 +18939,7 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W73" t="n">
         <v>1.16</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
         <v>3.3</v>
       </c>
       <c r="X74" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y74" t="n">
         <v>38</v>
@@ -19247,7 +19247,7 @@
         <v>1000</v>
       </c>
       <c r="AN74" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AO74" t="n">
         <v>1000</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -19423,16 +19423,16 @@
         <v>1.05</v>
       </c>
       <c r="N75" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="O75" t="n">
         <v>1.39</v>
       </c>
       <c r="P75" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="R75" t="n">
         <v>1.18</v>
@@ -19507,58 +19507,58 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="AV75" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AY75" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AZ75" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BF75" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BG75" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BH75" t="n">
         <v>1000</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
         <v>2.86</v>
       </c>
       <c r="G80" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H80" t="n">
         <v>2.62</v>
@@ -20690,31 +20690,31 @@
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N80" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="O80" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P80" t="n">
         <v>1.72</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="R80" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S80" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T80" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U80" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V80" t="n">
         <v>1.52</v>
@@ -20723,106 +20723,106 @@
         <v>1.45</v>
       </c>
       <c r="X80" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y80" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z80" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA80" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB80" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC80" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD80" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE80" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF80" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG80" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH80" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI80" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK80" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL80" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM80" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN80" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO80" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU80" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV80" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW80" t="n">
         <v>1.03</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC80" t="n">
         <v>1.03</v>
       </c>
       <c r="BD80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF80" t="n">
         <v>1.01</v>
@@ -20831,68 +20831,68 @@
         <v>1.01</v>
       </c>
       <c r="BH80" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI80" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="BJ80" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BK80" t="n">
-        <v>1.61</v>
+        <v>5.8</v>
       </c>
       <c r="BL80" t="n">
         <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>1.83</v>
+        <v>12.5</v>
       </c>
       <c r="BN80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO80" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP80" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ80" t="n">
-        <v>1.73</v>
+        <v>9</v>
       </c>
       <c r="BR80" t="n">
         <v>1000</v>
       </c>
       <c r="BS80" t="n">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="BT80" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU80" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BV80" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW80" t="n">
-        <v>1.73</v>
+        <v>8.6</v>
       </c>
       <c r="BX80" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="BZ80" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA80" t="n">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -20914,246 +20914,246 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="G81" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>2.84</v>
       </c>
       <c r="J81" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K81" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L81" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M81" t="n">
         <v>1.08</v>
       </c>
       <c r="N81" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O81" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P81" t="n">
         <v>1.76</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R81" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S81" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T81" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="U81" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V81" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="W81" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="X81" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y81" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z81" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA81" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB81" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC81" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD81" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE81" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF81" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG81" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH81" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI81" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK81" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL81" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM81" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN81" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO81" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU81" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV81" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW81" t="n">
         <v>1.03</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA81" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC81" t="n">
         <v>1.03</v>
       </c>
       <c r="BD81" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF81" t="n">
         <v>1.01</v>
       </c>
       <c r="BG81" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH81" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI81" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ81" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK81" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL81" t="n">
         <v>1000</v>
       </c>
       <c r="BM81" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN81" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO81" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP81" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ81" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR81" t="n">
         <v>1000</v>
       </c>
       <c r="BS81" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT81" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU81" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV81" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW81" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX81" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY81" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -21168,246 +21168,246 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="G82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H82" t="n">
         <v>3.2</v>
       </c>
-      <c r="H82" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I82" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="K82" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L82" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="M82" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N82" t="n">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="O82" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="P82" t="n">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="R82" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="S82" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="T82" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="U82" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="V82" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W82" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X82" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y82" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Z82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ82" t="n">
         <v>20</v>
       </c>
-      <c r="AA82" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ82" t="n">
+      <c r="BA82" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD82" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR82" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE82" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG82" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH82" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI82" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ82" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK82" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL82" t="n">
         <v>1000</v>
       </c>
       <c r="BM82" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN82" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO82" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP82" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ82" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR82" t="n">
         <v>1000</v>
       </c>
       <c r="BS82" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT82" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU82" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV82" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW82" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX82" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY82" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ82" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA82" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -21422,175 +21422,175 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="H83" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K83" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L83" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M83" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N83" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="O83" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="P83" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="R83" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S83" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="T83" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="U83" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="V83" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W83" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="X83" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y83" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z83" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA83" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB83" t="n">
         <v>10</v>
       </c>
       <c r="AC83" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP83" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD83" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF83" t="n">
+      <c r="AQ83" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR83" t="n">
         <v>21</v>
       </c>
-      <c r="AG83" t="n">
+      <c r="AS83" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC83" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH83" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO83" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP83" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AR83" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS83" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT83" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AU83" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AV83" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW83" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX83" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY83" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ83" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB83" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BC83" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BD83" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="BE83" t="n">
-        <v>2.26</v>
+        <v>5.3</v>
       </c>
       <c r="BF83" t="n">
-        <v>2.26</v>
+        <v>15</v>
       </c>
       <c r="BG83" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="BH83" t="n">
         <v>1000</v>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>
@@ -21850,7 +21850,7 @@
         <v>3.05</v>
       </c>
       <c r="BI84" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ84" t="n">
         <v>11</v>
@@ -21908,7 +21908,515 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-29 22:15:05</t>
+          <t>2026-05-30 00:40:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I85" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X85" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB85" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:40:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Club Oriental de La Paz</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Tacuarembo</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N86" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CB86" t="inlineStr">
+        <is>
+          <t>2026-05-30 00:40:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -887,7 +887,7 @@
         <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
         <v>1.87</v>
@@ -896,7 +896,7 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.44</v>
@@ -908,7 +908,7 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -926,7 +926,7 @@
         <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
         <v>65</v>
@@ -938,7 +938,7 @@
         <v>7.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>40</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>3.5</v>
@@ -1138,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
         <v>1.66</v>
@@ -1159,7 +1159,7 @@
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
         <v>1.71</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>2.04</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>3.9</v>
@@ -1389,13 +1389,13 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1404,16 +1404,16 @@
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W4" t="n">
         <v>1.33</v>
@@ -1425,7 +1425,7 @@
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
         <v>34</v>
@@ -1467,7 +1467,7 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO4" t="n">
         <v>21</v>
@@ -1512,7 +1512,7 @@
         <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
         <v>1.01</v>
@@ -1521,10 +1521,10 @@
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="I5" t="n">
         <v>1.92</v>
@@ -1634,7 +1634,7 @@
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
         <v>1.86</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
@@ -2136,7 +2136,7 @@
         <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -2151,7 +2151,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>1.36</v>
@@ -2160,10 +2160,10 @@
         <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
         <v>3.7</v>
@@ -2175,7 +2175,7 @@
         <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2256,10 +2256,10 @@
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
         <v>11.5</v>
@@ -2268,16 +2268,16 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
         <v>4.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>1.63</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2638,76 +2638,76 @@
         <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA9" t="n">
         <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>80</v>
@@ -2719,55 +2719,55 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
         <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW9" t="n">
         <v>4.7</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
         <v>7.8</v>
@@ -2779,10 +2779,10 @@
         <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD9" t="n">
         <v>4.4</v>
@@ -2791,19 +2791,19 @@
         <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG9" t="n">
         <v>4.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2815,31 +2815,31 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW9" t="n">
         <v>1.01</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="G10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.19</v>
@@ -2922,67 +2922,67 @@
         <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="W10" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB10" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG10" t="n">
         <v>14</v>
       </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ10" t="n">
         <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>36</v>
@@ -2994,22 +2994,22 @@
         <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3021,7 +3021,7 @@
         <v>19.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3030,31 +3030,31 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>27</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
         <v>8.800000000000001</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS10" t="n">
         <v>7.4</v>
       </c>
       <c r="BT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BW10" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BX10" t="n">
         <v>25</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -3173,10 +3173,10 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
@@ -3194,7 +3194,7 @@
         <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X11" t="n">
         <v>15.5</v>
@@ -3287,7 +3287,7 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
         <v>25</v>
@@ -3296,7 +3296,7 @@
         <v>4.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
         <v>18.5</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5.4</v>
@@ -3329,7 +3329,7 @@
         <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>8.800000000000001</v>
@@ -3338,7 +3338,7 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>6.2</v>
@@ -3350,13 +3350,13 @@
         <v>26</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>32</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
         <v>3.6</v>
@@ -3406,7 +3406,7 @@
         <v>2.14</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.85</v>
@@ -3421,67 +3421,67 @@
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
         <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
         <v>2.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W12" t="n">
         <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y12" t="n">
         <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA12" t="n">
         <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -3493,7 +3493,7 @@
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
         <v>65</v>
@@ -3520,7 +3520,7 @@
         <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -3532,13 +3532,13 @@
         <v>25</v>
       </c>
       <c r="AY12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BB12" t="n">
         <v>50</v>
@@ -3550,13 +3550,13 @@
         <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH12" t="n">
         <v>4.3</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G13" t="n">
         <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I13" t="n">
         <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3693,13 +3693,13 @@
         <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
         <v>1.55</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.17</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.13</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>2.54</v>
       </c>
       <c r="I17" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
@@ -4715,7 +4715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
         <v>1.51</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
         <v>1.99</v>
@@ -4990,7 +4990,7 @@
         <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>30</v>
@@ -5035,10 +5035,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
         <v>6.4</v>
@@ -5050,10 +5050,10 @@
         <v>17.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>7.6</v>
@@ -5062,7 +5062,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
         <v>11.5</v>
@@ -5071,22 +5071,22 @@
         <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="n">
         <v>3.4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
         <v>11.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -5208,13 +5208,13 @@
         <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T19" t="n">
         <v>1.46</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>110</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.05</v>
@@ -5477,10 +5477,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -5707,7 +5707,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
@@ -5716,13 +5716,13 @@
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R21" t="n">
         <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
@@ -5731,10 +5731,10 @@
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
         <v>19.5</v>
@@ -5761,7 +5761,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -5773,7 +5773,7 @@
         <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -5785,7 +5785,7 @@
         <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO21" t="n">
         <v>100</v>
@@ -5797,22 +5797,22 @@
         <v>15.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV21" t="n">
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>9.199999999999999</v>
@@ -5824,7 +5824,7 @@
         <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
         <v>12.5</v>
@@ -5833,16 +5833,16 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
         <v>2.86</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
@@ -6215,7 +6215,7 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.24</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
         <v>1.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
         <v>1.18</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -7001,11 +7001,11 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.48</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X26" t="n">
         <v>1000</v>
       </c>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -7207,118 +7207,118 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="S27" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
         <v>1.03</v>
@@ -7327,37 +7327,37 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
         <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
         <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
         <v>1.03</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -7494,13 +7494,13 @@
         <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S28" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G29" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H29" t="n">
         <v>3.05</v>
@@ -7763,10 +7763,10 @@
         <v>1.94</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
         <v>12</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="H30" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="J30" t="n">
         <v>2.9</v>
@@ -7993,16 +7993,16 @@
         <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="P30" t="n">
         <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
@@ -8014,13 +8014,13 @@
         <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W30" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="X30" t="n">
         <v>10.5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -8226,19 +8226,19 @@
         <v>2.22</v>
       </c>
       <c r="G31" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q31" t="n">
         <v>2.14</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -8498,19 +8498,19 @@
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
@@ -8534,7 +8534,7 @@
         <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
         <v>1000</v>
@@ -8543,34 +8543,34 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
@@ -8579,7 +8579,7 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -8597,10 +8597,10 @@
         <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
         <v>1.01</v>
@@ -8609,10 +8609,10 @@
         <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
         <v>1.01</v>
@@ -8621,10 +8621,10 @@
         <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
         <v>1.01</v>
@@ -8633,7 +8633,7 @@
         <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
         <v>1.01</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
         <v>3.95</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G34" t="n">
         <v>1.85</v>
@@ -8997,7 +8997,7 @@
         <v>5.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K34" t="n">
         <v>3.85</v>
@@ -9012,10 +9012,10 @@
         <v>3.95</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P34" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
         <v>1.9</v>
@@ -9054,10 +9054,10 @@
         <v>9.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
@@ -9105,7 +9105,7 @@
         <v>40</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU34" t="n">
         <v>7.6</v>
@@ -9114,7 +9114,7 @@
         <v>18</v>
       </c>
       <c r="AW34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX34" t="n">
         <v>9.800000000000001</v>
@@ -9123,7 +9123,7 @@
         <v>9</v>
       </c>
       <c r="AZ34" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA34" t="n">
         <v>32</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9248,7 @@
         <v>2.12</v>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J35" t="n">
         <v>3.6</v>
@@ -9404,22 +9404,22 @@
         <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BJ35" t="n">
         <v>12.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BN35" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO35" t="n">
         <v>4.7</v>
@@ -9428,41 +9428,41 @@
         <v>38</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BR35" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="BT35" t="n">
         <v>6.8</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BV35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW35" t="n">
-        <v>9.6</v>
+        <v>1.77</v>
       </c>
       <c r="BX35" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="BZ35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -9493,22 +9493,22 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G36" t="n">
         <v>2.76</v>
       </c>
-      <c r="G36" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H36" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>3.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -9517,13 +9517,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O36" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q36" t="n">
         <v>1.48</v>
@@ -9538,121 +9538,121 @@
         <v>1.4</v>
       </c>
       <c r="U36" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V36" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W36" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="X36" t="n">
         <v>30</v>
       </c>
       <c r="Y36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA36" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AB36" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF36" t="n">
         <v>25</v>
       </c>
-      <c r="AF36" t="n">
-        <v>29</v>
-      </c>
       <c r="AG36" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH36" t="n">
         <v>15</v>
       </c>
       <c r="AI36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ36" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK36" t="n">
         <v>28</v>
       </c>
       <c r="AL36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM36" t="n">
         <v>60</v>
       </c>
       <c r="AN36" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR36" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY36" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BF36" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH36" t="n">
         <v>1000</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I37" t="n">
         <v>1.97</v>
@@ -9768,10 +9768,10 @@
         <v>1.23</v>
       </c>
       <c r="M37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N37" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
         <v>1.18</v>
@@ -9786,7 +9786,7 @@
         <v>1.62</v>
       </c>
       <c r="S37" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T37" t="n">
         <v>1.55</v>
@@ -9825,7 +9825,7 @@
         <v>22</v>
       </c>
       <c r="AF37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG37" t="n">
         <v>21</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -10255,16 +10255,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G39" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>4.2</v>
@@ -10276,28 +10276,28 @@
         <v>1.22</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O39" t="n">
         <v>1.15</v>
       </c>
       <c r="P39" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S39" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U39" t="n">
         <v>2.6</v>
@@ -10306,49 +10306,49 @@
         <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>36</v>
       </c>
       <c r="Y39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z39" t="n">
         <v>40</v>
       </c>
       <c r="AA39" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB39" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE39" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF39" t="n">
         <v>18.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL39" t="n">
         <v>29</v>
@@ -10357,16 +10357,16 @@
         <v>65</v>
       </c>
       <c r="AN39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP39" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR39" t="n">
         <v>1.03</v>
@@ -10381,7 +10381,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW39" t="n">
         <v>1.01</v>
@@ -10399,7 +10399,7 @@
         <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC39" t="n">
         <v>13</v>
@@ -10411,10 +10411,10 @@
         <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH39" t="n">
         <v>5</v>
@@ -10432,53 +10432,53 @@
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO39" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP39" t="n">
         <v>13</v>
       </c>
       <c r="BQ39" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR39" t="n">
         <v>21</v>
       </c>
       <c r="BS39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT39" t="n">
         <v>8</v>
       </c>
       <c r="BU39" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BV39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX39" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ39" t="n">
         <v>13.5</v>
       </c>
       <c r="CA39" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G40" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H40" t="n">
         <v>4.7</v>
@@ -10542,7 +10542,7 @@
         <v>2.12</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R40" t="n">
         <v>1.4</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W40" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -10763,22 +10763,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G41" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H41" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I41" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10787,22 +10787,22 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P41" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10811,10 +10811,10 @@
         <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         <v>1.47</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I42" t="n">
         <v>990</v>
@@ -11032,7 +11032,7 @@
         <v>1.03</v>
       </c>
       <c r="K42" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -11041,25 +11041,25 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>1.09</v>
       </c>
       <c r="P42" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R42" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="S42" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T42" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U42" t="n">
         <v>1.11</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -11295,22 +11295,22 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q43" t="n">
         <v>1.02</v>
       </c>
       <c r="R43" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S43" t="n">
-        <v>1.02</v>
+        <v>1.7</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -11528,13 +11528,13 @@
         <v>2.5</v>
       </c>
       <c r="G44" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H44" t="n">
         <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
         <v>3.3</v>
@@ -11576,7 +11576,7 @@
         <v>1.51</v>
       </c>
       <c r="W44" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>110</v>
       </c>
       <c r="J45" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K45" t="n">
         <v>950</v>
@@ -11803,13 +11803,13 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
         <v>1.13</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q45" t="n">
         <v>1.13</v>
@@ -11827,10 +11827,10 @@
         <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
         <v>4.6</v>
       </c>
       <c r="L46" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
@@ -12063,13 +12063,13 @@
         <v>1.34</v>
       </c>
       <c r="P46" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
         <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
         <v>3.65</v>
@@ -12081,7 +12081,7 @@
         <v>1.78</v>
       </c>
       <c r="V46" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
         <v>2.5</v>
@@ -12099,10 +12099,10 @@
         <v>280</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD46" t="n">
         <v>34</v>
@@ -12135,25 +12135,25 @@
         <v>200</v>
       </c>
       <c r="AN46" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO46" t="n">
         <v>210</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AQ46" t="n">
         <v>14.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="AU46" t="n">
         <v>8</v>
@@ -12162,37 +12162,37 @@
         <v>19.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX46" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AY46" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB46" t="n">
         <v>11</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF46" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH46" t="n">
         <v>3.4</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G47" t="n">
         <v>1.39</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.4</v>
       </c>
       <c r="H47" t="n">
         <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J47" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.25</v>
@@ -12311,7 +12311,7 @@
         <v>1.04</v>
       </c>
       <c r="N47" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O47" t="n">
         <v>1.19</v>
@@ -12320,7 +12320,7 @@
         <v>2.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R47" t="n">
         <v>1.62</v>
@@ -12338,37 +12338,37 @@
         <v>1.09</v>
       </c>
       <c r="W47" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="X47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y47" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Z47" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA47" t="n">
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC47" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD47" t="n">
         <v>38</v>
       </c>
       <c r="AE47" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AF47" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AG47" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH47" t="n">
         <v>26</v>
@@ -12377,7 +12377,7 @@
         <v>120</v>
       </c>
       <c r="AJ47" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK47" t="n">
         <v>14</v>
@@ -12389,7 +12389,7 @@
         <v>140</v>
       </c>
       <c r="AN47" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO47" t="n">
         <v>160</v>
@@ -12401,10 +12401,10 @@
         <v>34</v>
       </c>
       <c r="AR47" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AT47" t="n">
         <v>9.4</v>
@@ -12428,7 +12428,7 @@
         <v>19.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="BB47" t="n">
         <v>10</v>
@@ -12440,13 +12440,13 @@
         <v>11</v>
       </c>
       <c r="BE47" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH47" t="n">
         <v>4.4</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -12547,13 +12547,13 @@
         <v>1.58</v>
       </c>
       <c r="H48" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K48" t="n">
         <v>4.5</v>
@@ -12577,7 +12577,7 @@
         <v>1.96</v>
       </c>
       <c r="R48" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S48" t="n">
         <v>3.45</v>
@@ -12586,13 +12586,13 @@
         <v>2.04</v>
       </c>
       <c r="U48" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V48" t="n">
         <v>1.14</v>
       </c>
       <c r="W48" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X48" t="n">
         <v>14.5</v>
@@ -12640,7 +12640,7 @@
         <v>42</v>
       </c>
       <c r="AM48" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN48" t="n">
         <v>9.800000000000001</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -12795,19 +12795,19 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G49" t="n">
         <v>5.1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I49" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J49" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K49" t="n">
         <v>3.6</v>
@@ -12819,7 +12819,7 @@
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>1.38</v>
@@ -12828,7 +12828,7 @@
         <v>1.85</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R49" t="n">
         <v>1.31</v>
@@ -12843,16 +12843,16 @@
         <v>1.97</v>
       </c>
       <c r="V49" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X49" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Z49" t="n">
         <v>12</v>
@@ -12891,13 +12891,13 @@
         <v>70</v>
       </c>
       <c r="AL49" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="n">
         <v>130</v>
       </c>
       <c r="AN49" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO49" t="n">
         <v>17.5</v>
@@ -12918,16 +12918,16 @@
         <v>13.5</v>
       </c>
       <c r="AU49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV49" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW49" t="n">
         <v>19</v>
       </c>
       <c r="AX49" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AY49" t="n">
         <v>17.5</v>
@@ -12948,10 +12948,10 @@
         <v>55</v>
       </c>
       <c r="BE49" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>9.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="BG49" t="n">
         <v>13.5</v>
@@ -12960,65 +12960,65 @@
         <v>1000</v>
       </c>
       <c r="BI49" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BJ49" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK49" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BL49" t="n">
         <v>1000</v>
       </c>
       <c r="BM49" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BN49" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO49" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP49" t="n">
         <v>1000</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BR49" t="n">
         <v>1000</v>
       </c>
       <c r="BS49" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BT49" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU49" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV49" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW49" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BX49" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY49" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G50" t="n">
         <v>1.45</v>
@@ -13064,16 +13064,16 @@
         <v>5.4</v>
       </c>
       <c r="K50" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M50" t="n">
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O50" t="n">
         <v>1.2</v>
@@ -13085,10 +13085,10 @@
         <v>1.59</v>
       </c>
       <c r="R50" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S50" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
         <v>1.82</v>
@@ -13100,13 +13100,13 @@
         <v>1.13</v>
       </c>
       <c r="W50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z50" t="n">
         <v>75</v>
@@ -13115,7 +13115,7 @@
         <v>260</v>
       </c>
       <c r="AB50" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC50" t="n">
         <v>14</v>
@@ -13127,7 +13127,7 @@
         <v>110</v>
       </c>
       <c r="AF50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG50" t="n">
         <v>10.5</v>
@@ -13163,10 +13163,10 @@
         <v>28</v>
       </c>
       <c r="AR50" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT50" t="n">
         <v>9.4</v>
@@ -13178,7 +13178,7 @@
         <v>26</v>
       </c>
       <c r="AW50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX50" t="n">
         <v>9</v>
@@ -13190,7 +13190,7 @@
         <v>20</v>
       </c>
       <c r="BA50" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB50" t="n">
         <v>11.5</v>
@@ -13202,77 +13202,77 @@
         <v>25</v>
       </c>
       <c r="BE50" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF50" t="n">
         <v>5</v>
       </c>
       <c r="BG50" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH50" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI50" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="BJ50" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK50" t="n">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="BL50" t="n">
         <v>1000</v>
       </c>
       <c r="BM50" t="n">
-        <v>3.4</v>
+        <v>12.5</v>
       </c>
       <c r="BN50" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BO50" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="BP50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ50" t="n">
         <v>12</v>
       </c>
-      <c r="BQ50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BT50" t="n">
-        <v>16</v>
-      </c>
-      <c r="BU50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BV50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BX50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BZ50" t="n">
-        <v>17.5</v>
-      </c>
       <c r="CA50" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G51" t="n">
         <v>3.3</v>
@@ -13312,13 +13312,13 @@
         <v>2.34</v>
       </c>
       <c r="I51" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J51" t="n">
         <v>3.75</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -13351,7 +13351,7 @@
         <v>2.24</v>
       </c>
       <c r="V51" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W51" t="n">
         <v>1.44</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -13557,16 +13557,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G52" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="H52" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I52" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J52" t="n">
         <v>4.6</v>
@@ -13578,7 +13578,7 @@
         <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N52" t="n">
         <v>5.2</v>
@@ -13593,7 +13593,7 @@
         <v>1.66</v>
       </c>
       <c r="R52" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S52" t="n">
         <v>2.46</v>
@@ -13602,121 +13602,121 @@
         <v>1.72</v>
       </c>
       <c r="U52" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V52" t="n">
         <v>1.2</v>
       </c>
       <c r="W52" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="X52" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Y52" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z52" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI52" t="n">
         <v>60</v>
       </c>
-      <c r="AA52" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD52" t="n">
+      <c r="AJ52" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL52" t="n">
         <v>28</v>
       </c>
-      <c r="AE52" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>34</v>
-      </c>
       <c r="AM52" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN52" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO52" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP52" t="n">
         <v>21</v>
       </c>
       <c r="AQ52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.6</v>
+        <v>40</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AT52" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU52" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.7</v>
+        <v>55</v>
       </c>
       <c r="AX52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY52" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ52" t="n">
         <v>17.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.6</v>
+        <v>50</v>
       </c>
       <c r="BB52" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC52" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC52" t="n">
-        <v>11</v>
-      </c>
       <c r="BD52" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.7</v>
+        <v>46</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
         <v>2.68</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J53" t="n">
         <v>3.45</v>
@@ -13859,7 +13859,7 @@
         <v>2.22</v>
       </c>
       <c r="V53" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W53" t="n">
         <v>1.53</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -14319,166 +14319,166 @@
         </is>
       </c>
       <c r="F55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J55" t="n">
         <v>3.9</v>
       </c>
-      <c r="G55" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X55" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="K55" t="n">
-        <v>950</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V55" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA55" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD55" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -15870,13 +15870,13 @@
         <v>3.3</v>
       </c>
       <c r="O61" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P61" t="n">
         <v>1.79</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R61" t="n">
         <v>1.3</v>
@@ -15888,7 +15888,7 @@
         <v>1.8</v>
       </c>
       <c r="U61" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V61" t="n">
         <v>1.48</v>
@@ -15993,7 +15993,7 @@
         <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE61" t="n">
         <v>1.01</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -16097,16 +16097,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G62" t="n">
         <v>2.4</v>
       </c>
       <c r="H62" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>3.35</v>
@@ -16115,25 +16115,25 @@
         <v>3.8</v>
       </c>
       <c r="L62" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M62" t="n">
         <v>1.08</v>
       </c>
       <c r="N62" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O62" t="n">
         <v>1.38</v>
       </c>
       <c r="P62" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q62" t="n">
         <v>2.12</v>
       </c>
       <c r="R62" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S62" t="n">
         <v>3.95</v>
@@ -16145,16 +16145,16 @@
         <v>1.94</v>
       </c>
       <c r="V62" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W62" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y62" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z62" t="n">
         <v>27</v>
@@ -16172,7 +16172,7 @@
         <v>970</v>
       </c>
       <c r="AE62" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF62" t="n">
         <v>970</v>
@@ -16181,7 +16181,7 @@
         <v>13.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI62" t="n">
         <v>65</v>
@@ -16208,37 +16208,37 @@
         <v>9.4</v>
       </c>
       <c r="AQ62" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT62" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU62" t="n">
         <v>6.4</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX62" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY62" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ62" t="n">
         <v>14</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB62" t="n">
         <v>1.01</v>
@@ -16247,16 +16247,16 @@
         <v>1.01</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF62" t="n">
         <v>16.5</v>
       </c>
       <c r="BG62" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH62" t="n">
         <v>3.2</v>
@@ -16280,7 +16280,7 @@
         <v>5.1</v>
       </c>
       <c r="BO62" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP62" t="n">
         <v>1000</v>
@@ -16298,7 +16298,7 @@
         <v>7.2</v>
       </c>
       <c r="BU62" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BV62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16360,7 @@
         <v>1.76</v>
       </c>
       <c r="I63" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J63" t="n">
         <v>3.4</v>
@@ -16399,10 +16399,10 @@
         <v>1.8</v>
       </c>
       <c r="V63" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W63" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X63" t="n">
         <v>13</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -17367,22 +17367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G67" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H67" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J67" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L67" t="n">
         <v>1.3</v>
@@ -17391,34 +17391,34 @@
         <v>1.06</v>
       </c>
       <c r="N67" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P67" t="n">
         <v>2.04</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="R67" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S67" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T67" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U67" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="V67" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W67" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X67" t="n">
         <v>16</v>
@@ -17430,7 +17430,7 @@
         <v>46</v>
       </c>
       <c r="AA67" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB67" t="n">
         <v>9.800000000000001</v>
@@ -17472,19 +17472,19 @@
         <v>11.5</v>
       </c>
       <c r="AO67" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP67" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR67" t="n">
         <v>10</v>
       </c>
       <c r="AS67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT67" t="n">
         <v>8.4</v>
@@ -17493,7 +17493,7 @@
         <v>7.4</v>
       </c>
       <c r="AV67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW67" t="n">
         <v>60</v>
@@ -17508,7 +17508,7 @@
         <v>17</v>
       </c>
       <c r="BA67" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BB67" t="n">
         <v>17</v>
@@ -17517,16 +17517,16 @@
         <v>17</v>
       </c>
       <c r="BD67" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE67" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF67" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG67" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH67" t="n">
         <v>3.85</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -17624,19 +17624,19 @@
         <v>2.1</v>
       </c>
       <c r="G68" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H68" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I68" t="n">
         <v>3.9</v>
       </c>
       <c r="J68" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K68" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -17654,7 +17654,7 @@
         <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R68" t="n">
         <v>1.38</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -17881,7 +17881,7 @@
         <v>2.18</v>
       </c>
       <c r="H69" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="I69" t="n">
         <v>5.8</v>
@@ -17890,7 +17890,7 @@
         <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L69" t="n">
         <v>1.43</v>
@@ -17899,7 +17899,7 @@
         <v>1.04</v>
       </c>
       <c r="N69" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>1.5</v>
@@ -17908,13 +17908,13 @@
         <v>1.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R69" t="n">
         <v>1.17</v>
       </c>
       <c r="S69" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -18129,64 +18129,64 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G70" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H70" t="n">
         <v>2.44</v>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="J70" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K70" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L70" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M70" t="n">
         <v>1.07</v>
       </c>
       <c r="N70" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O70" t="n">
         <v>1.3</v>
       </c>
       <c r="P70" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S70" t="n">
         <v>3.35</v>
       </c>
       <c r="T70" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V70" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W70" t="n">
         <v>1.43</v>
       </c>
       <c r="X70" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z70" t="n">
         <v>19</v>
@@ -18195,22 +18195,22 @@
         <v>40</v>
       </c>
       <c r="AB70" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC70" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD70" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG70" t="n">
         <v>14</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>16</v>
       </c>
       <c r="AH70" t="n">
         <v>19.5</v>
@@ -18222,7 +18222,7 @@
         <v>65</v>
       </c>
       <c r="AK70" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AL70" t="n">
         <v>55</v>
@@ -18231,25 +18231,25 @@
         <v>110</v>
       </c>
       <c r="AN70" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO70" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP70" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ70" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR70" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT70" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU70" t="n">
         <v>6.8</v>
@@ -18258,37 +18258,37 @@
         <v>10.5</v>
       </c>
       <c r="AW70" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX70" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX70" t="n">
-        <v>17</v>
-      </c>
       <c r="AY70" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ70" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA70" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC70" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD70" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG70" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BH70" t="n">
         <v>3.55</v>
@@ -18300,13 +18300,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK70" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN70" t="n">
         <v>6.8</v>
@@ -18318,13 +18318,13 @@
         <v>27</v>
       </c>
       <c r="BQ70" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR70" t="n">
         <v>40</v>
       </c>
       <c r="BS70" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT70" t="n">
         <v>5.5</v>
@@ -18333,7 +18333,7 @@
         <v>4</v>
       </c>
       <c r="BV70" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW70" t="n">
         <v>6.6</v>
@@ -18342,17 +18342,17 @@
         <v>32</v>
       </c>
       <c r="BY70" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ70" t="n">
         <v>27</v>
       </c>
       <c r="CA70" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -18383,22 +18383,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G71" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H71" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>3.2</v>
       </c>
       <c r="K71" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -18407,16 +18407,16 @@
         <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="O71" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P71" t="n">
         <v>1.61</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R71" t="n">
         <v>1.17</v>
@@ -18425,124 +18425,124 @@
         <v>4</v>
       </c>
       <c r="T71" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U71" t="n">
         <v>1.6</v>
       </c>
       <c r="V71" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W71" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X71" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y71" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z71" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA71" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB71" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY71" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC71" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ71" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK71" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW71" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AX71" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AY71" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AZ71" t="n">
-        <v>2.62</v>
+        <v>19</v>
       </c>
       <c r="BA71" t="n">
-        <v>2.86</v>
+        <v>8</v>
       </c>
       <c r="BB71" t="n">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BC71" t="n">
-        <v>2.66</v>
+        <v>6.6</v>
       </c>
       <c r="BD71" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="BE71" t="n">
-        <v>2.86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.86</v>
+        <v>17.5</v>
       </c>
       <c r="BG71" t="n">
-        <v>2.86</v>
+        <v>8</v>
       </c>
       <c r="BH71" t="n">
         <v>1000</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
         <v>1.3</v>
       </c>
       <c r="H72" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I72" t="n">
         <v>17</v>
@@ -18667,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -18891,22 +18891,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G73" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H73" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I73" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>3.3</v>
       </c>
       <c r="K73" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -18921,10 +18921,10 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -19169,13 +19169,13 @@
         <v>1.11</v>
       </c>
       <c r="N74" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P74" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q74" t="n">
         <v>2.6</v>
@@ -19190,7 +19190,7 @@
         <v>2.22</v>
       </c>
       <c r="U74" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V74" t="n">
         <v>1.19</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -19399,22 +19399,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="G75" t="n">
         <v>3.25</v>
       </c>
       <c r="H75" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="I75" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="J75" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="K75" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L75" t="n">
         <v>1.01</v>
@@ -19423,34 +19423,34 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="O75" t="n">
         <v>1.18</v>
       </c>
       <c r="P75" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R75" t="n">
         <v>1.58</v>
       </c>
       <c r="S75" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T75" t="n">
         <v>1.52</v>
       </c>
       <c r="U75" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V75" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W75" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X75" t="n">
         <v>29</v>
@@ -19462,7 +19462,7 @@
         <v>22</v>
       </c>
       <c r="AA75" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB75" t="n">
         <v>18</v>
@@ -19477,10 +19477,10 @@
         <v>25</v>
       </c>
       <c r="AF75" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG75" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH75" t="n">
         <v>15.5</v>
@@ -19489,76 +19489,76 @@
         <v>34</v>
       </c>
       <c r="AJ75" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK75" t="n">
         <v>29</v>
       </c>
       <c r="AL75" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM75" t="n">
         <v>65</v>
       </c>
       <c r="AN75" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AO75" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE75" t="n">
         <v>1.03</v>
       </c>
       <c r="BF75" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG75" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH75" t="n">
         <v>1000</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -19907,22 +19907,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G77" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H77" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J77" t="n">
         <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L77" t="n">
         <v>1.01</v>
@@ -19955,10 +19955,10 @@
         <v>1.01</v>
       </c>
       <c r="V77" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W77" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="X77" t="n">
         <v>1000</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -20191,10 +20191,10 @@
         <v>1.01</v>
       </c>
       <c r="P78" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R78" t="n">
         <v>1.22</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -20690,7 +20690,7 @@
         <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N80" t="n">
         <v>2.9</v>
@@ -20717,7 +20717,7 @@
         <v>1.01</v>
       </c>
       <c r="V80" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W80" t="n">
         <v>1.15</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -20923,64 +20923,64 @@
         </is>
       </c>
       <c r="F81" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H81" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O81" t="n">
         <v>1.32</v>
       </c>
-      <c r="G81" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H81" t="n">
-        <v>10</v>
-      </c>
-      <c r="I81" t="n">
-        <v>17</v>
-      </c>
-      <c r="J81" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K81" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1.28</v>
-      </c>
       <c r="P81" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R81" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T81" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="U81" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="V81" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W81" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="X81" t="n">
         <v>970</v>
       </c>
       <c r="Y81" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Z81" t="n">
         <v>1000</v>
@@ -20992,10 +20992,10 @@
         <v>970</v>
       </c>
       <c r="AC81" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD81" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AE81" t="n">
         <v>1000</v>
@@ -21007,7 +21007,7 @@
         <v>970</v>
       </c>
       <c r="AH81" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI81" t="n">
         <v>1000</v>
@@ -21031,58 +21031,58 @@
         <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU81" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV81" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AW81" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BA81" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BD81" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BF81" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG81" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BH81" t="n">
         <v>4.3</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -21198,25 +21198,25 @@
         <v>1.01</v>
       </c>
       <c r="M82" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N82" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="O82" t="n">
         <v>1.39</v>
       </c>
       <c r="P82" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="R82" t="n">
         <v>1.18</v>
       </c>
       <c r="S82" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="T82" t="n">
         <v>1.65</v>
@@ -21252,7 +21252,7 @@
         <v>970</v>
       </c>
       <c r="AE82" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF82" t="n">
         <v>26</v>
@@ -21285,58 +21285,58 @@
         <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AU82" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AV82" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AW82" t="n">
         <v>1.9</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="BA82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BD82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BG82" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BH82" t="n">
         <v>1000</v>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -21431,10 +21431,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G83" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H83" t="n">
         <v>4.1</v>
@@ -21560,7 +21560,7 @@
         <v>15</v>
       </c>
       <c r="AW83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX83" t="n">
         <v>10</v>
@@ -21572,7 +21572,7 @@
         <v>16.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB83" t="n">
         <v>19.5</v>
@@ -21581,7 +21581,7 @@
         <v>19</v>
       </c>
       <c r="BD83" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE83" t="n">
         <v>1.01</v>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -21685,22 +21685,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="G84" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H84" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I84" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="J84" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K84" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L84" t="n">
         <v>1.01</v>
@@ -21709,7 +21709,7 @@
         <v>1.05</v>
       </c>
       <c r="N84" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="O84" t="n">
         <v>1.29</v>
@@ -21721,22 +21721,22 @@
         <v>1.89</v>
       </c>
       <c r="R84" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="S84" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T84" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U84" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V84" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="W84" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X84" t="n">
         <v>1000</v>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -21942,16 +21942,16 @@
         <v>1.04</v>
       </c>
       <c r="G85" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H85" t="n">
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J85" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K85" t="n">
         <v>950</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -22196,22 +22196,22 @@
         <v>1.77</v>
       </c>
       <c r="G86" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H86" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I86" t="n">
         <v>5.3</v>
       </c>
       <c r="J86" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K86" t="n">
         <v>4.6</v>
       </c>
       <c r="L86" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="M86" t="n">
         <v>1.04</v>
@@ -22235,7 +22235,7 @@
         <v>2.64</v>
       </c>
       <c r="T86" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U86" t="n">
         <v>2.2</v>
@@ -22244,7 +22244,7 @@
         <v>1.23</v>
       </c>
       <c r="W86" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X86" t="n">
         <v>22</v>
@@ -22253,7 +22253,7 @@
         <v>22</v>
       </c>
       <c r="Z86" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA86" t="n">
         <v>130</v>
@@ -22364,13 +22364,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK86" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL86" t="n">
         <v>1000</v>
       </c>
       <c r="BM86" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN86" t="n">
         <v>4.8</v>
@@ -22382,16 +22382,16 @@
         <v>12</v>
       </c>
       <c r="BQ86" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR86" t="n">
         <v>24</v>
       </c>
       <c r="BS86" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT86" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU86" t="n">
         <v>4.7</v>
@@ -22406,17 +22406,17 @@
         <v>42</v>
       </c>
       <c r="BY86" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ86" t="n">
         <v>17.5</v>
       </c>
       <c r="CA86" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -22447,19 +22447,19 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G87" t="n">
         <v>3.15</v>
       </c>
       <c r="H87" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I87" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J87" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K87" t="n">
         <v>3.55</v>
@@ -22480,7 +22480,7 @@
         <v>1.72</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="R87" t="n">
         <v>1.27</v>
@@ -22498,7 +22498,7 @@
         <v>1.52</v>
       </c>
       <c r="W87" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X87" t="n">
         <v>14</v>
@@ -22534,10 +22534,10 @@
         <v>23</v>
       </c>
       <c r="AI87" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ87" t="n">
         <v>60</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>65</v>
       </c>
       <c r="AK87" t="n">
         <v>46</v>
@@ -22576,7 +22576,7 @@
         <v>9.4</v>
       </c>
       <c r="AW87" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX87" t="n">
         <v>14</v>
@@ -22594,19 +22594,19 @@
         <v>4</v>
       </c>
       <c r="BC87" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD87" t="n">
         <v>4</v>
       </c>
       <c r="BE87" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF87" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG87" t="n">
-        <v>3.85</v>
+        <v>23</v>
       </c>
       <c r="BH87" t="n">
         <v>3.15</v>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -22985,7 +22985,7 @@
         <v>1.37</v>
       </c>
       <c r="P89" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q89" t="n">
         <v>2.08</v>
@@ -23015,7 +23015,7 @@
         <v>12</v>
       </c>
       <c r="Z89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="n">
         <v>42</v>
@@ -23039,7 +23039,7 @@
         <v>16</v>
       </c>
       <c r="AH89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI89" t="n">
         <v>48</v>
@@ -23072,7 +23072,7 @@
         <v>12.5</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT89" t="n">
         <v>8.199999999999999</v>
@@ -23084,7 +23084,7 @@
         <v>9</v>
       </c>
       <c r="AW89" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX89" t="n">
         <v>14.5</v>
@@ -23096,22 +23096,22 @@
         <v>13</v>
       </c>
       <c r="BA89" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BB89" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC89" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD89" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE89" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF89" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG89" t="n">
         <v>20</v>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -23209,16 +23209,16 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G90" t="n">
         <v>2.8</v>
       </c>
       <c r="H90" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I90" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>2.88</v>
@@ -23242,13 +23242,13 @@
         <v>1.46</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="R90" t="n">
         <v>1.17</v>
       </c>
       <c r="S90" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T90" t="n">
         <v>2.14</v>
@@ -23432,7 +23432,7 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -23628,7 +23628,7 @@
         <v>3.05</v>
       </c>
       <c r="BI91" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="BJ91" t="n">
         <v>11</v>
@@ -23686,7 +23686,7 @@
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -23747,16 +23747,16 @@
         <v>1.32</v>
       </c>
       <c r="P92" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="R92" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S92" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T92" t="n">
         <v>1.8</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>
@@ -23974,16 +23974,16 @@
         <v>2.58</v>
       </c>
       <c r="G93" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="H93" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I93" t="n">
         <v>3.85</v>
       </c>
       <c r="J93" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="K93" t="n">
         <v>3.25</v>
@@ -24004,7 +24004,7 @@
         <v>1.53</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R93" t="n">
         <v>1.19</v>
@@ -24136,7 +24136,7 @@
         <v>2.76</v>
       </c>
       <c r="BI93" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="BJ93" t="n">
         <v>11.5</v>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>2026-05-30 03:07:22</t>
+          <t>2026-05-30 05:32:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-31.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -881,31 +881,31 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
         <v>3.6</v>
@@ -923,7 +923,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AC2" t="n">
         <v>14</v>
@@ -932,10 +932,10 @@
         <v>50</v>
       </c>
       <c r="AE2" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AF2" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -944,19 +944,19 @@
         <v>38</v>
       </c>
       <c r="AI2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AK2" t="n">
         <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AN2" t="n">
         <v>6.6</v>
@@ -965,43 +965,43 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT2" t="n">
         <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
         <v>6.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1010,43 +1010,43 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>14</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
         <v>3.55</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BP2" t="n">
         <v>8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
@@ -1058,19 +1058,19 @@
         <v>15.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
         <v>2.34</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>4.3</v>
@@ -1129,7 +1129,7 @@
         <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1141,10 +1141,10 @@
         <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1177,7 +1177,7 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
         <v>9</v>
@@ -1228,7 +1228,7 @@
         <v>19.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1240,7 +1240,7 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9.800000000000001</v>
@@ -1252,37 +1252,37 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.9</v>
       </c>
       <c r="BC3" t="n">
         <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
         <v>17.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,50 +1291,50 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
         <v>4.1</v>
@@ -1395,10 +1395,10 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="I5" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
@@ -1667,10 +1667,10 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>12</v>
@@ -1697,34 +1697,34 @@
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AK5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL5" t="n">
         <v>75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
         <v>11.5</v>
@@ -1733,10 +1733,10 @@
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>13</v>
@@ -1745,13 +1745,13 @@
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
         <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY5" t="n">
         <v>14.5</v>
@@ -1760,79 +1760,79 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.4</v>
+        <v>3.25</v>
       </c>
       <c r="BN5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -2038,7 +2038,7 @@
         <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
         <v>3.75</v>
@@ -2148,7 +2148,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
         <v>2.96</v>
@@ -2157,7 +2157,7 @@
         <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
         <v>2.14</v>
@@ -2178,67 +2178,67 @@
         <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
         <v>1.03</v>
@@ -2250,7 +2250,7 @@
         <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -2283,10 +2283,10 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -2402,97 +2402,97 @@
         <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
         <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AP8" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR8" t="n">
         <v>1.03</v>
@@ -2501,13 +2501,13 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU8" t="n">
         <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
@@ -2516,7 +2516,7 @@
         <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
         <v>1.03</v>
@@ -2537,7 +2537,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BG8" t="n">
         <v>12.5</v>
@@ -2546,7 +2546,7 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2564,31 +2564,31 @@
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
         <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="I9" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2662,7 +2662,7 @@
         <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -2889,46 +2889,46 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
         <v>4.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
         <v>1.76</v>
@@ -2937,7 +2937,7 @@
         <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.25</v>
@@ -2949,7 +2949,7 @@
         <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>32</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
         <v>6.2</v>
@@ -3409,7 +3409,7 @@
         <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.9</v>
@@ -3421,7 +3421,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
@@ -3430,7 +3430,7 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.43</v>
@@ -3439,7 +3439,7 @@
         <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U12" t="n">
         <v>1.98</v>
@@ -3448,7 +3448,7 @@
         <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -3490,7 +3490,7 @@
         <v>15.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
         <v>40</v>
@@ -3499,7 +3499,7 @@
         <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>120</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -3678,34 +3678,34 @@
         <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
         <v>32</v>
@@ -3714,19 +3714,19 @@
         <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE13" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
         <v>12.5</v>
@@ -3735,13 +3735,13 @@
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK13" t="n">
         <v>19</v>
@@ -3750,13 +3750,13 @@
         <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
         <v>15.5</v>
@@ -3771,22 +3771,22 @@
         <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW13" t="n">
         <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>15</v>
@@ -3810,7 +3810,7 @@
         <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH13" t="n">
         <v>4.3</v>
@@ -3834,10 +3834,10 @@
         <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ13" t="n">
         <v>7</v>
@@ -3849,10 +3849,10 @@
         <v>16</v>
       </c>
       <c r="BT13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
         <v>3.55</v>
@@ -3929,43 +3929,43 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
         <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>12.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
         <v>46</v>
@@ -3974,7 +3974,7 @@
         <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
         <v>14.5</v>
@@ -4013,19 +4013,19 @@
         <v>32</v>
       </c>
       <c r="AP14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -4034,34 +4034,34 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX14" t="n">
-        <v>4</v>
-      </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
         <v>19</v>
@@ -4070,19 +4070,19 @@
         <v>3.25</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="BN14" t="n">
         <v>6.2</v>
@@ -4091,7 +4091,7 @@
         <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ14" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT14" t="n">
         <v>5.5</v>
@@ -4118,17 +4118,17 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.35</v>
       </c>
       <c r="G15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
         <v>8.199999999999999</v>
@@ -4186,13 +4186,13 @@
         <v>4.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
         <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
         <v>1.52</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
@@ -4464,7 +4464,7 @@
         <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X16" t="n">
         <v>20</v>
@@ -4578,7 +4578,7 @@
         <v>3.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I17" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
@@ -4697,7 +4697,7 @@
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q17" t="n">
         <v>1.56</v>
@@ -4712,13 +4712,13 @@
         <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X17" t="n">
         <v>26</v>
@@ -4748,10 +4748,10 @@
         <v>26</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -4802,22 +4802,22 @@
         <v>21</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>26</v>
       </c>
       <c r="BC17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE17" t="n">
         <v>27</v>
@@ -4826,7 +4826,7 @@
         <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="n">
         <v>4.6</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G18" t="n">
         <v>2.54</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
         <v>3.2</v>
@@ -4936,7 +4936,7 @@
         <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
@@ -4957,7 +4957,7 @@
         <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
         <v>3.85</v>
@@ -5035,7 +5035,7 @@
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I19" t="n">
         <v>2.3</v>
@@ -5199,7 +5199,7 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
@@ -5220,16 +5220,16 @@
         <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y19" t="n">
         <v>14.5</v>
@@ -5241,7 +5241,7 @@
         <v>34</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
@@ -5253,7 +5253,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
@@ -5262,16 +5262,16 @@
         <v>14.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM19" t="n">
         <v>60</v>
@@ -5304,19 +5304,19 @@
         <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
         <v>46</v>
@@ -5325,13 +5325,13 @@
         <v>28</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG19" t="n">
         <v>10</v>
@@ -5343,7 +5343,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK19" t="n">
         <v>5.5</v>
@@ -5352,43 +5352,43 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP19" t="n">
         <v>23</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR19" t="n">
         <v>29</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT19" t="n">
         <v>5.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
         <v>15</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
         <v>2.78</v>
@@ -5459,22 +5459,22 @@
         <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
         <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V20" t="n">
         <v>1.54</v>
@@ -5570,7 +5570,7 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -5579,13 +5579,13 @@
         <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
         <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG20" t="n">
         <v>20</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v>1.33</v>
       </c>
       <c r="I21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="J21" t="n">
         <v>5.3</v>
@@ -5704,34 +5704,34 @@
         <v>1.24</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
         <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="W21" t="n">
         <v>1.08</v>
@@ -5740,7 +5740,7 @@
         <v>30</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>11</v>
@@ -5773,19 +5773,19 @@
         <v>44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AK21" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AL21" t="n">
         <v>150</v>
       </c>
       <c r="AM21" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AO21" t="n">
         <v>6.2</v>
@@ -5839,7 +5839,7 @@
         <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BG21" t="n">
         <v>4</v>
@@ -5863,7 +5863,7 @@
         <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BO21" t="n">
         <v>9.6</v>
@@ -5884,10 +5884,10 @@
         <v>4.1</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BV21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW21" t="n">
         <v>5.8</v>
@@ -5899,14 +5899,14 @@
         <v>16</v>
       </c>
       <c r="BZ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>4.4</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
         <v>1.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -5985,10 +5985,10 @@
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W22" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6099,68 +6099,68 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM22" t="n">
         <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -6206,13 +6206,13 @@
         <v>2.72</v>
       </c>
       <c r="K23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.54</v>
       </c>
       <c r="M23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N23" t="n">
         <v>2.4</v>
@@ -6221,22 +6221,22 @@
         <v>1.58</v>
       </c>
       <c r="P23" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V23" t="n">
         <v>1.44</v>
@@ -6245,16 +6245,16 @@
         <v>1.43</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
         <v>9.6</v>
@@ -6263,16 +6263,16 @@
         <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE23" t="n">
         <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -6281,10 +6281,10 @@
         <v>95</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL23" t="n">
         <v>95</v>
@@ -6293,19 +6293,19 @@
         <v>250</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS23" t="n">
         <v>1.03</v>
@@ -6317,16 +6317,16 @@
         <v>5.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
         <v>18.5</v>
@@ -6347,46 +6347,46 @@
         <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH23" t="n">
         <v>2.66</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="BJ23" t="n">
         <v>12</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.96</v>
+        <v>5.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO23" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
         <v>32</v>
       </c>
       <c r="BQ23" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>3.65</v>
+        <v>9.4</v>
       </c>
       <c r="BT23" t="n">
         <v>6</v>
@@ -6398,23 +6398,23 @@
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>3.65</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>3.65</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -6445,145 +6445,145 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.86</v>
+        <v>2.48</v>
       </c>
       <c r="G24" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="H24" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
         <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
         <v>22</v>
       </c>
       <c r="AA24" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC24" t="n">
         <v>10</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK24" t="n">
         <v>34</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN24" t="n">
         <v>25</v>
       </c>
-      <c r="AG24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>32</v>
-      </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS24" t="n">
         <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW24" t="n">
         <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
         <v>1.03</v>
@@ -6592,7 +6592,7 @@
         <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD24" t="n">
         <v>1.03</v>
@@ -6601,10 +6601,10 @@
         <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="J25" t="n">
         <v>2.92</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6735,7 +6735,7 @@
         <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
         <v>3.55</v>
@@ -6747,10 +6747,10 @@
         <v>1.75</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
         <v>2.74</v>
       </c>
       <c r="T26" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="U26" t="n">
         <v>2.4</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G27" t="n">
         <v>1.68</v>
@@ -7225,7 +7225,7 @@
         <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
@@ -7240,13 +7240,13 @@
         <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R27" t="n">
         <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
         <v>1.9</v>
@@ -7258,13 +7258,13 @@
         <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X27" t="n">
         <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
         <v>120</v>
@@ -7276,7 +7276,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
         <v>24</v>
@@ -7309,7 +7309,7 @@
         <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO27" t="n">
         <v>100</v>
@@ -7330,7 +7330,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV27" t="n">
         <v>19</v>
@@ -7360,16 +7360,16 @@
         <v>29</v>
       </c>
       <c r="BE27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI27" t="n">
         <v>3.25</v>
@@ -7378,13 +7378,13 @@
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN27" t="n">
         <v>4.4</v>
@@ -7396,41 +7396,41 @@
         <v>11.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR27" t="n">
         <v>26</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV27" t="n">
         <v>55</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ27" t="n">
         <v>19.5</v>
       </c>
       <c r="CA27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -7485,16 +7485,16 @@
         <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
         <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R28" t="n">
         <v>1.6</v>
@@ -7503,7 +7503,7 @@
         <v>2.42</v>
       </c>
       <c r="T28" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="U28" t="n">
         <v>2.28</v>
@@ -7620,7 +7620,7 @@
         <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
         <v>4.4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>1.65</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -7730,10 +7730,10 @@
         <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -7826,7 +7826,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>4.5</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
         <v>2.54</v>
       </c>
       <c r="I30" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -7990,19 +7990,19 @@
         <v>1.3</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
         <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="R30" t="n">
         <v>1.45</v>
@@ -8011,79 +8011,79 @@
         <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V30" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS30" t="n">
         <v>1.03</v>
@@ -8098,10 +8098,10 @@
         <v>9.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
@@ -8116,7 +8116,7 @@
         <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD30" t="n">
         <v>1.03</v>
@@ -8125,19 +8125,19 @@
         <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK30" t="n">
         <v>6.8</v>
@@ -8146,43 +8146,43 @@
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ30" t="n">
         <v>0</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -8223,112 +8223,112 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="G31" t="n">
-        <v>110</v>
+        <v>2.06</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I31" t="n">
-        <v>110</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P31" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP31" t="n">
         <v>1.03</v>
@@ -8358,10 +8358,10 @@
         <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA31" t="n">
         <v>1.03</v>
@@ -8379,74 +8379,74 @@
         <v>1.03</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -8501,13 +8501,13 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="O32" t="n">
         <v>1.18</v>
       </c>
       <c r="P32" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q32" t="n">
         <v>1.18</v>
@@ -8519,7 +8519,7 @@
         <v>1.18</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U32" t="n">
         <v>1.11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -8740,13 +8740,13 @@
         <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.23</v>
@@ -8755,13 +8755,13 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="Q33" t="n">
         <v>1.5</v>
@@ -8773,13 +8773,13 @@
         <v>2.26</v>
       </c>
       <c r="T33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U33" t="n">
         <v>2.42</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W33" t="n">
         <v>2.38</v>
@@ -8866,7 +8866,7 @@
         <v>10</v>
       </c>
       <c r="AY33" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ33" t="n">
         <v>4.2</v>
@@ -8893,7 +8893,7 @@
         <v>4.9</v>
       </c>
       <c r="BH33" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BI33" t="n">
         <v>3.5</v>
@@ -8908,7 +8908,7 @@
         <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="BN33" t="n">
         <v>1000</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW34" t="n">
         <v>1.03</v>
@@ -9126,7 +9126,7 @@
         <v>10.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB34" t="n">
         <v>21</v>
@@ -9135,7 +9135,7 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BE34" t="n">
         <v>1.03</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -9245,16 +9245,16 @@
         <v>3.1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I35" t="n">
         <v>2.64</v>
       </c>
       <c r="J35" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K35" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.22</v>
@@ -9278,16 +9278,16 @@
         <v>1.64</v>
       </c>
       <c r="S35" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T35" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U35" t="n">
         <v>2.62</v>
       </c>
       <c r="V35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W35" t="n">
         <v>1.5</v>
@@ -9302,7 +9302,7 @@
         <v>22</v>
       </c>
       <c r="AA35" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB35" t="n">
         <v>19.5</v>
@@ -9398,7 +9398,7 @@
         <v>11</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -9502,10 +9502,10 @@
         <v>2.78</v>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J36" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K36" t="n">
         <v>3.2</v>
@@ -9517,7 +9517,7 @@
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
         <v>1.52</v>
@@ -9526,7 +9526,7 @@
         <v>1.56</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R36" t="n">
         <v>1.2</v>
@@ -9535,13 +9535,13 @@
         <v>5.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V36" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.45</v>
@@ -9592,7 +9592,7 @@
         <v>75</v>
       </c>
       <c r="AM36" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN36" t="n">
         <v>60</v>
@@ -9658,7 +9658,7 @@
         <v>2.78</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.5</v>
@@ -9670,7 +9670,7 @@
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN36" t="n">
         <v>6.2</v>
@@ -9697,13 +9697,13 @@
         <v>4.5</v>
       </c>
       <c r="BV36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW36" t="n">
         <v>20</v>
       </c>
       <c r="BX36" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY36" t="n">
         <v>36</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="G37" t="n">
         <v>2.8</v>
@@ -9756,16 +9756,16 @@
         <v>3.05</v>
       </c>
       <c r="I37" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J37" t="n">
         <v>3.05</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
@@ -9777,10 +9777,10 @@
         <v>1.43</v>
       </c>
       <c r="P37" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R37" t="n">
         <v>1.25</v>
@@ -9795,7 +9795,7 @@
         <v>1.94</v>
       </c>
       <c r="V37" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W37" t="n">
         <v>1.55</v>
@@ -9810,10 +9810,10 @@
         <v>24</v>
       </c>
       <c r="AA37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
         <v>8.199999999999999</v>
@@ -9822,7 +9822,7 @@
         <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF37" t="n">
         <v>18.5</v>
@@ -9834,7 +9834,7 @@
         <v>22</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ37" t="n">
         <v>44</v>
@@ -9855,58 +9855,58 @@
         <v>55</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU37" t="n">
         <v>6.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AX37" t="n">
-        <v>14</v>
+        <v>5.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC37" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF37" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BG37" t="n">
         <v>7</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH37" t="n">
         <v>3</v>
@@ -9924,13 +9924,13 @@
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN37" t="n">
         <v>5.4</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -10010,13 +10010,13 @@
         <v>3.6</v>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J38" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L38" t="n">
         <v>1.38</v>
@@ -10025,7 +10025,7 @@
         <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>1.4</v>
@@ -10034,16 +10034,16 @@
         <v>1.81</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
         <v>2</v>
@@ -10052,10 +10052,10 @@
         <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X38" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y38" t="n">
         <v>15</v>
@@ -10070,10 +10070,10 @@
         <v>9</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD38" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE38" t="n">
         <v>60</v>
@@ -10106,10 +10106,10 @@
         <v>26</v>
       </c>
       <c r="AO38" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ38" t="n">
         <v>10.5</v>
@@ -10127,7 +10127,7 @@
         <v>7</v>
       </c>
       <c r="AV38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW38" t="n">
         <v>1.03</v>
@@ -10157,10 +10157,10 @@
         <v>1.03</v>
       </c>
       <c r="BF38" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG38" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BH38" t="n">
         <v>3.25</v>
@@ -10178,7 +10178,7 @@
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN38" t="n">
         <v>5.2</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -10261,16 +10261,16 @@
         <v>1.54</v>
       </c>
       <c r="H39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I39" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J39" t="n">
         <v>4.6</v>
       </c>
       <c r="K39" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.27</v>
@@ -10333,10 +10333,10 @@
         <v>120</v>
       </c>
       <c r="AF39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG39" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH39" t="n">
         <v>27</v>
@@ -10363,7 +10363,7 @@
         <v>150</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.01</v>
@@ -10393,7 +10393,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
         <v>1.03</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G40" t="n">
         <v>3.75</v>
@@ -10674,7 +10674,7 @@
         <v>3.9</v>
       </c>
       <c r="BI40" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -10802,13 +10802,13 @@
         <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V41" t="n">
         <v>1.21</v>
@@ -10841,7 +10841,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG41" t="n">
         <v>12.5</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -11023,10 +11023,10 @@
         <v>1.88</v>
       </c>
       <c r="H42" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I42" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>3.8</v>
@@ -11050,7 +11050,7 @@
         <v>2.14</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R42" t="n">
         <v>1.45</v>
@@ -11065,7 +11065,7 @@
         <v>2.14</v>
       </c>
       <c r="V42" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W42" t="n">
         <v>2.12</v>
@@ -11074,10 +11074,10 @@
         <v>23</v>
       </c>
       <c r="Y42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA42" t="n">
         <v>130</v>
@@ -11122,7 +11122,7 @@
         <v>12</v>
       </c>
       <c r="AO42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP42" t="n">
         <v>13.5</v>
@@ -11137,7 +11137,7 @@
         <v>1.03</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU42" t="n">
         <v>7</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
         <v>1.22</v>
       </c>
       <c r="M43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N43" t="n">
         <v>6.2</v>
@@ -11310,10 +11310,10 @@
         <v>1.71</v>
       </c>
       <c r="S43" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U43" t="n">
         <v>2.66</v>
@@ -11328,37 +11328,37 @@
         <v>36</v>
       </c>
       <c r="Y43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z43" t="n">
         <v>40</v>
       </c>
       <c r="AA43" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB43" t="n">
         <v>18</v>
       </c>
       <c r="AC43" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD43" t="n">
         <v>20</v>
       </c>
       <c r="AE43" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF43" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG43" t="n">
         <v>13</v>
       </c>
       <c r="AH43" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI43" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ43" t="n">
         <v>26</v>
@@ -11370,7 +11370,7 @@
         <v>29</v>
       </c>
       <c r="AM43" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN43" t="n">
         <v>8.6</v>
@@ -11427,7 +11427,7 @@
         <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG43" t="n">
         <v>17.5</v>
@@ -11436,7 +11436,7 @@
         <v>5</v>
       </c>
       <c r="BI43" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ43" t="n">
         <v>8.800000000000001</v>
@@ -11448,10 +11448,10 @@
         <v>1000</v>
       </c>
       <c r="BM43" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN43" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO43" t="n">
         <v>4.2</v>
@@ -11460,13 +11460,13 @@
         <v>13</v>
       </c>
       <c r="BQ43" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR43" t="n">
         <v>21</v>
       </c>
       <c r="BS43" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT43" t="n">
         <v>8</v>
@@ -11478,23 +11478,23 @@
         <v>26</v>
       </c>
       <c r="BW43" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX43" t="n">
         <v>30</v>
       </c>
       <c r="BY43" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ43" t="n">
         <v>13.5</v>
       </c>
       <c r="CA43" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -11525,22 +11525,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G44" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="H44" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J44" t="n">
         <v>6.2</v>
       </c>
       <c r="K44" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -11549,25 +11549,25 @@
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O44" t="n">
         <v>1.11</v>
       </c>
       <c r="P44" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q44" t="n">
         <v>1.32</v>
       </c>
       <c r="R44" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
         <v>1.84</v>
       </c>
       <c r="T44" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U44" t="n">
         <v>2.42</v>
@@ -11576,7 +11576,7 @@
         <v>1.11</v>
       </c>
       <c r="W44" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="X44" t="n">
         <v>55</v>
@@ -11588,10 +11588,10 @@
         <v>100</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB44" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC44" t="n">
         <v>18.5</v>
@@ -11603,10 +11603,10 @@
         <v>100</v>
       </c>
       <c r="AF44" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG44" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH44" t="n">
         <v>25</v>
@@ -11615,10 +11615,10 @@
         <v>75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL44" t="n">
         <v>28</v>
@@ -11627,7 +11627,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AO44" t="n">
         <v>75</v>
@@ -11648,7 +11648,7 @@
         <v>12.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AV44" t="n">
         <v>1.03</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
         <v>3.85</v>
       </c>
       <c r="G45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H45" t="n">
         <v>1.82</v>
@@ -11800,28 +11800,28 @@
         <v>1.23</v>
       </c>
       <c r="M45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O45" t="n">
         <v>1.18</v>
       </c>
       <c r="P45" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q45" t="n">
         <v>1.53</v>
       </c>
       <c r="R45" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S45" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T45" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U45" t="n">
         <v>2.48</v>
@@ -11830,7 +11830,7 @@
         <v>2.02</v>
       </c>
       <c r="W45" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X45" t="n">
         <v>32</v>
@@ -11839,10 +11839,10 @@
         <v>16.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB45" t="n">
         <v>27</v>
@@ -11851,10 +11851,10 @@
         <v>13</v>
       </c>
       <c r="AD45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="n">
         <v>42</v>
@@ -11884,7 +11884,7 @@
         <v>36</v>
       </c>
       <c r="AO45" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP45" t="n">
         <v>19</v>
@@ -11944,37 +11944,37 @@
         <v>4.6</v>
       </c>
       <c r="BI45" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ45" t="n">
         <v>9</v>
       </c>
       <c r="BK45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN45" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP45" t="n">
         <v>29</v>
       </c>
       <c r="BQ45" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR45" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS45" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT45" t="n">
         <v>5.2</v>
@@ -11986,23 +11986,23 @@
         <v>12.5</v>
       </c>
       <c r="BW45" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX45" t="n">
         <v>21</v>
       </c>
       <c r="BY45" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ45" t="n">
         <v>14.5</v>
       </c>
       <c r="CA45" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -12033,28 +12033,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G46" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I46" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J46" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="K46" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N46" t="n">
         <v>6</v>
@@ -12063,34 +12063,34 @@
         <v>1.16</v>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R46" t="n">
         <v>1.69</v>
       </c>
       <c r="S46" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U46" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W46" t="n">
         <v>1.55</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.56</v>
       </c>
       <c r="X46" t="n">
         <v>30</v>
       </c>
       <c r="Y46" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z46" t="n">
         <v>26</v>
@@ -12102,7 +12102,7 @@
         <v>19.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD46" t="n">
         <v>15</v>
@@ -12132,13 +12132,13 @@
         <v>29</v>
       </c>
       <c r="AM46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN46" t="n">
         <v>14.5</v>
       </c>
       <c r="AO46" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP46" t="n">
         <v>5.1</v>
@@ -12195,68 +12195,68 @@
         <v>10</v>
       </c>
       <c r="BH46" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BJ46" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BN46" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP46" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BR46" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT46" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV46" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX46" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O47" t="n">
         <v>1.13</v>
@@ -12323,7 +12323,7 @@
         <v>1.4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S47" t="n">
         <v>2.02</v>
@@ -12485,10 +12485,10 @@
         <v>16.5</v>
       </c>
       <c r="BT47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV47" t="n">
         <v>15</v>
@@ -12506,11 +12506,11 @@
         <v>12.5</v>
       </c>
       <c r="CA47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -12559,13 +12559,13 @@
         <v>3.85</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M48" t="n">
         <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O48" t="n">
         <v>1.3</v>
@@ -12643,7 +12643,7 @@
         <v>110</v>
       </c>
       <c r="AN48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO48" t="n">
         <v>80</v>
@@ -12661,7 +12661,7 @@
         <v>40</v>
       </c>
       <c r="AT48" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU48" t="n">
         <v>7.6</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -13052,43 +13052,43 @@
         <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="H50" t="n">
         <v>2.7</v>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J50" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K50" t="n">
         <v>4</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M50" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="O50" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P50" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T50" t="n">
         <v>1.47</v>
@@ -13097,10 +13097,10 @@
         <v>2.18</v>
       </c>
       <c r="V50" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W50" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>6.6</v>
       </c>
       <c r="I51" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>3.9</v>
@@ -13333,7 +13333,7 @@
         <v>1.34</v>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q51" t="n">
         <v>2</v>
@@ -13441,7 +13441,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA51" t="n">
         <v>5</v>
@@ -13450,7 +13450,7 @@
         <v>11</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BD51" t="n">
         <v>4.7</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>110</v>
       </c>
       <c r="J52" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K52" t="n">
         <v>950</v>
@@ -13581,13 +13581,13 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O52" t="n">
         <v>1.12</v>
       </c>
       <c r="P52" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q52" t="n">
         <v>1.12</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -13814,19 +13814,19 @@
         <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H53" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I53" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="J53" t="n">
         <v>3.75</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13835,7 +13835,7 @@
         <v>1.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O53" t="n">
         <v>1.26</v>
@@ -13856,10 +13856,10 @@
         <v>1.66</v>
       </c>
       <c r="U53" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V53" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W53" t="n">
         <v>1.44</v>
@@ -13889,7 +13889,7 @@
         <v>24</v>
       </c>
       <c r="AF53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG53" t="n">
         <v>970</v>
@@ -13901,7 +13901,7 @@
         <v>34</v>
       </c>
       <c r="AJ53" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK53" t="n">
         <v>34</v>
@@ -13919,16 +13919,16 @@
         <v>18.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ53" t="n">
         <v>10.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS53" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT53" t="n">
         <v>12.5</v>
@@ -13940,31 +13940,31 @@
         <v>10</v>
       </c>
       <c r="AW53" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX53" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY53" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB53" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD53" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC53" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE53" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF53" t="n">
         <v>19.5</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
         <v>3.1</v>
       </c>
       <c r="H54" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I54" t="n">
         <v>2.72</v>
@@ -14080,7 +14080,7 @@
         <v>3.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L54" t="n">
         <v>1.32</v>
@@ -14107,13 +14107,13 @@
         <v>3.25</v>
       </c>
       <c r="T54" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U54" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V54" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W54" t="n">
         <v>1.48</v>
@@ -14230,7 +14230,7 @@
         <v>3.55</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="BJ54" t="n">
         <v>9.199999999999999</v>
@@ -14242,7 +14242,7 @@
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN54" t="n">
         <v>6</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
         <v>1.59</v>
       </c>
       <c r="G55" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H55" t="n">
         <v>5.5</v>
@@ -14331,10 +14331,10 @@
         <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K55" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L55" t="n">
         <v>1.26</v>
@@ -14361,16 +14361,16 @@
         <v>2.48</v>
       </c>
       <c r="T55" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U55" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V55" t="n">
         <v>1.2</v>
       </c>
       <c r="W55" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X55" t="n">
         <v>24</v>
@@ -14403,7 +14403,7 @@
         <v>10.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI55" t="n">
         <v>65</v>
@@ -14436,7 +14436,7 @@
         <v>40</v>
       </c>
       <c r="AS55" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT55" t="n">
         <v>10</v>
@@ -14472,13 +14472,13 @@
         <v>24</v>
       </c>
       <c r="BE55" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF55" t="n">
         <v>6.2</v>
       </c>
       <c r="BG55" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH55" t="n">
         <v>4.5</v>
@@ -14487,7 +14487,7 @@
         <v>3.35</v>
       </c>
       <c r="BJ55" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK55" t="n">
         <v>7.2</v>
@@ -14502,13 +14502,13 @@
         <v>4.7</v>
       </c>
       <c r="BO55" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP55" t="n">
         <v>11</v>
       </c>
       <c r="BQ55" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR55" t="n">
         <v>22</v>
@@ -14526,10 +14526,10 @@
         <v>44</v>
       </c>
       <c r="BW55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BX55" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY55" t="n">
         <v>30</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
         <v>3.6</v>
       </c>
       <c r="K56" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L56" t="n">
         <v>1.43</v>
@@ -14621,7 +14621,7 @@
         <v>2.02</v>
       </c>
       <c r="V56" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W56" t="n">
         <v>1.36</v>
@@ -14642,7 +14642,7 @@
         <v>13</v>
       </c>
       <c r="AC56" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD56" t="n">
         <v>11.5</v>
@@ -14651,7 +14651,7 @@
         <v>25</v>
       </c>
       <c r="AF56" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AG56" t="n">
         <v>16.5</v>
@@ -14660,10 +14660,10 @@
         <v>21</v>
       </c>
       <c r="AI56" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ56" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK56" t="n">
         <v>50</v>
@@ -14729,7 +14729,7 @@
         <v>12.5</v>
       </c>
       <c r="BF56" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG56" t="n">
         <v>16</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -14830,19 +14830,19 @@
         <v>1.43</v>
       </c>
       <c r="G57" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H57" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J57" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K57" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L57" t="n">
         <v>1.23</v>
@@ -14860,7 +14860,7 @@
         <v>2.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R57" t="n">
         <v>1.61</v>
@@ -14869,25 +14869,25 @@
         <v>2.48</v>
       </c>
       <c r="T57" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U57" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V57" t="n">
         <v>1.13</v>
       </c>
       <c r="W57" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X57" t="n">
         <v>27</v>
       </c>
       <c r="Y57" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z57" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA57" t="n">
         <v>260</v>
@@ -14938,13 +14938,13 @@
         <v>22</v>
       </c>
       <c r="AQ57" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AR57" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS57" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT57" t="n">
         <v>9.4</v>
@@ -14956,7 +14956,7 @@
         <v>26</v>
       </c>
       <c r="AW57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX57" t="n">
         <v>9</v>
@@ -14980,7 +14980,7 @@
         <v>25</v>
       </c>
       <c r="BE57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF57" t="n">
         <v>5</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -15081,19 +15081,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G58" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H58" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J58" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K58" t="n">
         <v>5.5</v>
@@ -15102,10 +15102,10 @@
         <v>1.29</v>
       </c>
       <c r="M58" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N58" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O58" t="n">
         <v>1.19</v>
@@ -15120,25 +15120,25 @@
         <v>1.62</v>
       </c>
       <c r="S58" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T58" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U58" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V58" t="n">
         <v>1.1</v>
       </c>
       <c r="W58" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="X58" t="n">
         <v>25</v>
       </c>
       <c r="Y58" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z58" t="n">
         <v>90</v>
@@ -15147,16 +15147,16 @@
         <v>330</v>
       </c>
       <c r="AB58" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC58" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD58" t="n">
         <v>36</v>
       </c>
       <c r="AE58" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF58" t="n">
         <v>9.800000000000001</v>
@@ -15165,10 +15165,10 @@
         <v>11</v>
       </c>
       <c r="AH58" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI58" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ58" t="n">
         <v>12</v>
@@ -15186,31 +15186,31 @@
         <v>5.2</v>
       </c>
       <c r="AO58" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP58" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AQ58" t="n">
         <v>34</v>
       </c>
       <c r="AR58" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS58" t="n">
         <v>14</v>
       </c>
-      <c r="AS58" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AT58" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU58" t="n">
         <v>10.5</v>
       </c>
       <c r="AV58" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX58" t="n">
         <v>8.4</v>
@@ -15222,7 +15222,7 @@
         <v>19.5</v>
       </c>
       <c r="BA58" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB58" t="n">
         <v>10</v>
@@ -15231,16 +15231,16 @@
         <v>12.5</v>
       </c>
       <c r="BD58" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BE58" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF58" t="n">
         <v>4.6</v>
       </c>
       <c r="BG58" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BH58" t="n">
         <v>4.4</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -15341,10 +15341,10 @@
         <v>5.2</v>
       </c>
       <c r="H59" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I59" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J59" t="n">
         <v>3.5</v>
@@ -15356,13 +15356,13 @@
         <v>1.45</v>
       </c>
       <c r="M59" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O59" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P59" t="n">
         <v>1.87</v>
@@ -15371,16 +15371,16 @@
         <v>2.1</v>
       </c>
       <c r="R59" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S59" t="n">
         <v>3.8</v>
       </c>
       <c r="T59" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U59" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V59" t="n">
         <v>2.06</v>
@@ -15389,22 +15389,22 @@
         <v>1.24</v>
       </c>
       <c r="X59" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y59" t="n">
         <v>9.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA59" t="n">
         <v>23</v>
       </c>
       <c r="AB59" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC59" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD59" t="n">
         <v>12</v>
@@ -15416,13 +15416,13 @@
         <v>36</v>
       </c>
       <c r="AG59" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI59" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ59" t="n">
         <v>120</v>
@@ -15434,7 +15434,7 @@
         <v>95</v>
       </c>
       <c r="AM59" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN59" t="n">
         <v>85</v>
@@ -15443,7 +15443,7 @@
         <v>15</v>
       </c>
       <c r="AP59" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ59" t="n">
         <v>7.6</v>
@@ -15467,10 +15467,10 @@
         <v>19</v>
       </c>
       <c r="AX59" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY59" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ59" t="n">
         <v>18</v>
@@ -15479,19 +15479,19 @@
         <v>36</v>
       </c>
       <c r="BB59" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC59" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BD59" t="n">
         <v>55</v>
       </c>
       <c r="BE59" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF59" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="BG59" t="n">
         <v>13</v>
@@ -15500,22 +15500,22 @@
         <v>3.2</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ59" t="n">
         <v>10.5</v>
       </c>
       <c r="BK59" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN59" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO59" t="n">
         <v>6</v>
@@ -15524,41 +15524,41 @@
         <v>1000</v>
       </c>
       <c r="BQ59" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR59" t="n">
         <v>1000</v>
       </c>
       <c r="BS59" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT59" t="n">
         <v>4.5</v>
       </c>
       <c r="BU59" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV59" t="n">
         <v>14</v>
       </c>
       <c r="BW59" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX59" t="n">
         <v>32</v>
       </c>
       <c r="BY59" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ59" t="n">
         <v>28</v>
       </c>
       <c r="CA59" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G60" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H60" t="n">
         <v>6.8</v>
@@ -15607,7 +15607,7 @@
         <v>4.5</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M60" t="n">
         <v>1.07</v>
@@ -15619,7 +15619,7 @@
         <v>1.33</v>
       </c>
       <c r="P60" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q60" t="n">
         <v>1.96</v>
@@ -15634,13 +15634,13 @@
         <v>2.06</v>
       </c>
       <c r="U60" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V60" t="n">
         <v>1.14</v>
       </c>
       <c r="W60" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X60" t="n">
         <v>14.5</v>
@@ -15661,7 +15661,7 @@
         <v>10.5</v>
       </c>
       <c r="AD60" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE60" t="n">
         <v>130</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
         <v>3.55</v>
       </c>
       <c r="G63" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H63" t="n">
         <v>1.88</v>
@@ -16384,7 +16384,7 @@
         <v>2.48</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="R63" t="n">
         <v>1.61</v>
@@ -16402,7 +16402,7 @@
         <v>1.96</v>
       </c>
       <c r="W63" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
         <v>30</v>
@@ -16507,74 +16507,74 @@
         <v>3.9</v>
       </c>
       <c r="BF63" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BG63" t="n">
         <v>3.65</v>
       </c>
       <c r="BH63" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ63" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK63" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL63" t="n">
         <v>1000</v>
       </c>
       <c r="BM63" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN63" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO63" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP63" t="n">
         <v>1000</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BR63" t="n">
         <v>1000</v>
       </c>
       <c r="BS63" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT63" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU63" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV63" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW63" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX63" t="n">
         <v>1000</v>
       </c>
       <c r="BY63" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -17532,19 +17532,19 @@
         <v>3.25</v>
       </c>
       <c r="BI67" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ67" t="n">
         <v>1000</v>
       </c>
       <c r="BK67" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL67" t="n">
         <v>1000</v>
       </c>
       <c r="BM67" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BN67" t="n">
         <v>5.8</v>
@@ -17556,13 +17556,13 @@
         <v>1000</v>
       </c>
       <c r="BQ67" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR67" t="n">
         <v>1000</v>
       </c>
       <c r="BS67" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="BT67" t="n">
         <v>5.9</v>
@@ -17580,17 +17580,17 @@
         <v>1000</v>
       </c>
       <c r="BY67" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BZ67" t="n">
         <v>1000</v>
       </c>
       <c r="CA67" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -17639,7 +17639,7 @@
         <v>3.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M68" t="n">
         <v>1.08</v>
@@ -17651,7 +17651,7 @@
         <v>1.38</v>
       </c>
       <c r="P68" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q68" t="n">
         <v>2.12</v>
@@ -17786,7 +17786,7 @@
         <v>3.2</v>
       </c>
       <c r="BI68" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ68" t="n">
         <v>10.5</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
         <v>3.85</v>
       </c>
       <c r="L69" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M69" t="n">
         <v>1.09</v>
@@ -18034,7 +18034,7 @@
         <v>6.2</v>
       </c>
       <c r="BG69" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BH69" t="n">
         <v>3.2</v>
@@ -18046,31 +18046,31 @@
         <v>11.5</v>
       </c>
       <c r="BK69" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL69" t="n">
         <v>1000</v>
       </c>
       <c r="BM69" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN69" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO69" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP69" t="n">
         <v>1000</v>
       </c>
       <c r="BQ69" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR69" t="n">
         <v>1000</v>
       </c>
       <c r="BS69" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT69" t="n">
         <v>4.4</v>
@@ -18082,23 +18082,23 @@
         <v>13.5</v>
       </c>
       <c r="BW69" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX69" t="n">
         <v>1000</v>
       </c>
       <c r="BY69" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ69" t="n">
         <v>1000</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -18162,7 +18162,7 @@
         <v>1.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R70" t="n">
         <v>1.12</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -18637,22 +18637,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G72" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="H72" t="n">
         <v>4.2</v>
       </c>
       <c r="I72" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J72" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K72" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -18685,10 +18685,10 @@
         <v>1.01</v>
       </c>
       <c r="V72" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W72" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -18894,13 +18894,13 @@
         <v>1.02</v>
       </c>
       <c r="G73" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H73" t="n">
         <v>1.02</v>
       </c>
       <c r="I73" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J73" t="n">
         <v>1.02</v>
@@ -18915,13 +18915,13 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O73" t="n">
         <v>1.32</v>
       </c>
       <c r="P73" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q73" t="n">
         <v>1.32</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -19148,22 +19148,22 @@
         <v>1.7</v>
       </c>
       <c r="G74" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I74" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>3.8</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L74" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M74" t="n">
         <v>1.06</v>
@@ -19172,31 +19172,31 @@
         <v>4.2</v>
       </c>
       <c r="O74" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P74" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R74" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S74" t="n">
         <v>3.05</v>
       </c>
       <c r="T74" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U74" t="n">
         <v>2.14</v>
       </c>
       <c r="V74" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W74" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X74" t="n">
         <v>17</v>
@@ -19205,25 +19205,25 @@
         <v>24</v>
       </c>
       <c r="Z74" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AA74" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB74" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC74" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD74" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE74" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF74" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG74" t="n">
         <v>9.6</v>
@@ -19235,10 +19235,10 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK74" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>18</v>
       </c>
       <c r="AL74" t="n">
         <v>30</v>
@@ -19247,22 +19247,22 @@
         <v>110</v>
       </c>
       <c r="AN74" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO74" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP74" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ74" t="n">
         <v>21</v>
       </c>
       <c r="AR74" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS74" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT74" t="n">
         <v>8</v>
@@ -19274,22 +19274,22 @@
         <v>20</v>
       </c>
       <c r="AW74" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX74" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY74" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ74" t="n">
         <v>18</v>
       </c>
       <c r="BA74" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB74" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC74" t="n">
         <v>15.5</v>
@@ -19298,16 +19298,16 @@
         <v>23</v>
       </c>
       <c r="BE74" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG74" t="n">
         <v>14</v>
       </c>
-      <c r="BF74" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG74" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH74" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI74" t="n">
         <v>3.25</v>
@@ -19316,59 +19316,59 @@
         <v>10.5</v>
       </c>
       <c r="BK74" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL74" t="n">
         <v>1000</v>
       </c>
       <c r="BM74" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BN74" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO74" t="n">
         <v>3.45</v>
       </c>
       <c r="BP74" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ74" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS74" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT74" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU74" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV74" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BW74" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX74" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY74" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ74" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA74" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
         <v>2.26</v>
       </c>
       <c r="H75" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I75" t="n">
         <v>3.8</v>
@@ -19414,25 +19414,25 @@
         <v>3.55</v>
       </c>
       <c r="K75" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L75" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M75" t="n">
         <v>1.06</v>
       </c>
       <c r="N75" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O75" t="n">
         <v>1.29</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="R75" t="n">
         <v>1.38</v>
@@ -19441,7 +19441,7 @@
         <v>3.2</v>
       </c>
       <c r="T75" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U75" t="n">
         <v>2.18</v>
@@ -19453,13 +19453,13 @@
         <v>1.79</v>
       </c>
       <c r="X75" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y75" t="n">
         <v>970</v>
       </c>
       <c r="Z75" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA75" t="n">
         <v>75</v>
@@ -19513,10 +19513,10 @@
         <v>11</v>
       </c>
       <c r="AR75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS75" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT75" t="n">
         <v>4</v>
@@ -19525,104 +19525,104 @@
         <v>7.2</v>
       </c>
       <c r="AV75" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW75" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX75" t="n">
         <v>10.5</v>
       </c>
       <c r="AY75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ75" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA75" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB75" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC75" t="n">
         <v>17</v>
       </c>
       <c r="BD75" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE75" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF75" t="n">
         <v>12</v>
       </c>
       <c r="BG75" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU75" t="n">
         <v>5.4</v>
       </c>
-      <c r="BH75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV75" t="n">
         <v>1000</v>
       </c>
       <c r="BW75" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX75" t="n">
         <v>1000</v>
       </c>
       <c r="BY75" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BZ75" t="n">
         <v>1000</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -19653,19 +19653,19 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G76" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H76" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I76" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J76" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K76" t="n">
         <v>950</v>
@@ -19677,13 +19677,13 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O76" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P76" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q76" t="n">
         <v>1.32</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
         <v>4.5</v>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J77" t="n">
         <v>3.1</v>
@@ -19925,7 +19925,7 @@
         <v>3.5</v>
       </c>
       <c r="L77" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
         <v>1.11</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G78" t="n">
         <v>2.14</v>
@@ -20173,55 +20173,55 @@
         <v>6</v>
       </c>
       <c r="J78" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K78" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L78" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M78" t="n">
         <v>1.14</v>
       </c>
       <c r="N78" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P78" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="R78" t="n">
         <v>1.17</v>
       </c>
       <c r="S78" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T78" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U78" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V78" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W78" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X78" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y78" t="n">
         <v>14</v>
       </c>
       <c r="Z78" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA78" t="n">
         <v>190</v>
@@ -20230,10 +20230,10 @@
         <v>6.4</v>
       </c>
       <c r="AC78" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD78" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE78" t="n">
         <v>130</v>
@@ -20242,46 +20242,46 @@
         <v>11</v>
       </c>
       <c r="AG78" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH78" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK78" t="n">
         <v>34</v>
       </c>
-      <c r="AI78" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>36</v>
-      </c>
       <c r="AL78" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM78" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN78" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO78" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP78" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ78" t="n">
         <v>10</v>
       </c>
       <c r="AR78" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS78" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT78" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU78" t="n">
         <v>6.4</v>
@@ -20290,76 +20290,76 @@
         <v>18</v>
       </c>
       <c r="AW78" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX78" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY78" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ78" t="n">
         <v>21</v>
       </c>
       <c r="BA78" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB78" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC78" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF78" t="n">
         <v>21</v>
       </c>
-      <c r="BD78" t="n">
+      <c r="BG78" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK78" t="n">
         <v>6</v>
       </c>
-      <c r="BE78" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF78" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG78" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH78" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI78" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ78" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BL78" t="n">
         <v>1000</v>
       </c>
       <c r="BM78" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN78" t="n">
         <v>4.6</v>
       </c>
       <c r="BO78" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP78" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ78" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR78" t="n">
         <v>1000</v>
       </c>
       <c r="BS78" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT78" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BT78" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BU78" t="n">
         <v>4.8</v>
@@ -20368,23 +20368,23 @@
         <v>1000</v>
       </c>
       <c r="BW78" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX78" t="n">
         <v>1000</v>
       </c>
       <c r="BY78" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ78" t="n">
         <v>1000</v>
       </c>
       <c r="CA78" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
         <v>2.08</v>
       </c>
       <c r="G79" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H79" t="n">
         <v>4.3</v>
@@ -20466,7 +20466,7 @@
         <v>1.27</v>
       </c>
       <c r="W79" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X79" t="n">
         <v>10.5</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -20675,7 +20675,7 @@
         <v>1.29</v>
       </c>
       <c r="H80" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I80" t="n">
         <v>14</v>
@@ -20693,7 +20693,7 @@
         <v>1.04</v>
       </c>
       <c r="N80" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O80" t="n">
         <v>1.23</v>
@@ -20702,7 +20702,7 @@
         <v>2.26</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R80" t="n">
         <v>1.51</v>
@@ -20717,7 +20717,7 @@
         <v>1.66</v>
       </c>
       <c r="V80" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W80" t="n">
         <v>4.4</v>
@@ -20738,7 +20738,7 @@
         <v>8.6</v>
       </c>
       <c r="AC80" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD80" t="n">
         <v>55</v>
@@ -20753,7 +20753,7 @@
         <v>12.5</v>
       </c>
       <c r="AH80" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI80" t="n">
         <v>230</v>
@@ -20771,25 +20771,25 @@
         <v>250</v>
       </c>
       <c r="AN80" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO80" t="n">
         <v>390</v>
       </c>
       <c r="AP80" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ80" t="n">
         <v>36</v>
       </c>
       <c r="AR80" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS80" t="n">
         <v>12.5</v>
       </c>
       <c r="AT80" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU80" t="n">
         <v>13</v>
@@ -20798,7 +20798,7 @@
         <v>40</v>
       </c>
       <c r="AW80" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX80" t="n">
         <v>6.6</v>
@@ -20810,10 +20810,10 @@
         <v>25</v>
       </c>
       <c r="BA80" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BB80" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC80" t="n">
         <v>13.5</v>
@@ -20822,13 +20822,13 @@
         <v>30</v>
       </c>
       <c r="BE80" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF80" t="n">
         <v>4.5</v>
       </c>
       <c r="BG80" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH80" t="n">
         <v>4.2</v>
@@ -20846,7 +20846,7 @@
         <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN80" t="n">
         <v>3.6</v>
@@ -20876,13 +20876,13 @@
         <v>1000</v>
       </c>
       <c r="BW80" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX80" t="n">
         <v>1000</v>
       </c>
       <c r="BY80" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ80" t="n">
         <v>11</v>
@@ -20892,7 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
         <v>1.39</v>
       </c>
       <c r="M81" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N81" t="n">
         <v>3.3</v>
@@ -20953,16 +20953,16 @@
         <v>1.39</v>
       </c>
       <c r="P81" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R81" t="n">
         <v>1.3</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T81" t="n">
         <v>1.89</v>
@@ -20977,13 +20977,13 @@
         <v>1.81</v>
       </c>
       <c r="X81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y81" t="n">
         <v>13</v>
       </c>
       <c r="Z81" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA81" t="n">
         <v>80</v>
@@ -21004,7 +21004,7 @@
         <v>13.5</v>
       </c>
       <c r="AG81" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH81" t="n">
         <v>19.5</v>
@@ -21013,10 +21013,10 @@
         <v>70</v>
       </c>
       <c r="AJ81" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL81" t="n">
         <v>50</v>
@@ -21061,7 +21061,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ81" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA81" t="n">
         <v>1.03</v>
@@ -21079,7 +21079,7 @@
         <v>1.03</v>
       </c>
       <c r="BF81" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG81" t="n">
         <v>44</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21186,7 @@
         <v>2.44</v>
       </c>
       <c r="I82" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J82" t="n">
         <v>3.35</v>
@@ -21294,10 +21294,10 @@
         <v>14</v>
       </c>
       <c r="AS82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT82" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU82" t="n">
         <v>7</v>
@@ -21400,7 +21400,7 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -21908,7 +21908,7 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -21939,19 +21939,19 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G85" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H85" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I85" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J85" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K85" t="n">
         <v>950</v>
@@ -21963,13 +21963,13 @@
         <v>1.01</v>
       </c>
       <c r="N85" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O85" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P85" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q85" t="n">
         <v>1.3</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -22193,7 +22193,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G86" t="n">
         <v>2.3</v>
@@ -22202,19 +22202,19 @@
         <v>3.4</v>
       </c>
       <c r="I86" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="J86" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="K86" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
       </c>
       <c r="M86" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N86" t="n">
         <v>1.89</v>
@@ -22241,7 +22241,7 @@
         <v>1.01</v>
       </c>
       <c r="V86" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W86" t="n">
         <v>1.76</v>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -22474,10 +22474,10 @@
         <v>3.05</v>
       </c>
       <c r="O87" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P87" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q87" t="n">
         <v>2.1</v>
@@ -22486,13 +22486,13 @@
         <v>1.28</v>
       </c>
       <c r="S87" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T87" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U87" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V87" t="n">
         <v>1.38</v>
@@ -22516,7 +22516,7 @@
         <v>10.5</v>
       </c>
       <c r="AC87" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD87" t="n">
         <v>17</v>
@@ -22558,7 +22558,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR87" t="n">
         <v>1.03</v>
@@ -22567,7 +22567,7 @@
         <v>1.03</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU87" t="n">
         <v>1.03</v>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -22785,7 +22785,7 @@
         <v>12.5</v>
       </c>
       <c r="AH88" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI88" t="n">
         <v>90</v>
@@ -22815,10 +22815,10 @@
         <v>13</v>
       </c>
       <c r="AR88" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS88" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT88" t="n">
         <v>6.4</v>
@@ -22830,7 +22830,7 @@
         <v>15</v>
       </c>
       <c r="AW88" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX88" t="n">
         <v>8</v>
@@ -22842,7 +22842,7 @@
         <v>14.5</v>
       </c>
       <c r="BA88" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB88" t="n">
         <v>13.5</v>
@@ -22851,16 +22851,16 @@
         <v>13.5</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE88" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF88" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG88" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH88" t="n">
         <v>3.6</v>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -23212,13 +23212,13 @@
         <v>2.7</v>
       </c>
       <c r="G90" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H90" t="n">
         <v>2.72</v>
       </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>2.94</v>
@@ -23432,7 +23432,7 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -23469,61 +23469,61 @@
         <v>1.41</v>
       </c>
       <c r="H91" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="J91" t="n">
         <v>4.6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
       </c>
       <c r="M91" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S91" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V91" t="n">
         <v>1.07</v>
       </c>
-      <c r="N91" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S91" t="n">
+      <c r="W91" t="n">
         <v>3.3</v>
-      </c>
-      <c r="T91" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W91" t="n">
-        <v>3.45</v>
       </c>
       <c r="X91" t="n">
         <v>970</v>
       </c>
       <c r="Y91" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z91" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA91" t="n">
         <v>1000</v>
@@ -23535,7 +23535,7 @@
         <v>970</v>
       </c>
       <c r="AD91" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AE91" t="n">
         <v>1000</v>
@@ -23547,7 +23547,7 @@
         <v>970</v>
       </c>
       <c r="AH91" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AI91" t="n">
         <v>1000</v>
@@ -23571,112 +23571,112 @@
         <v>1000</v>
       </c>
       <c r="AP91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>4.9</v>
+        <v>2.42</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AU91" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AV91" t="n">
-        <v>5.2</v>
+        <v>2.46</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.13</v>
+        <v>2.46</v>
       </c>
       <c r="AX91" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AY91" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AZ91" t="n">
-        <v>5.1</v>
+        <v>2.42</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="BB91" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BC91" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD91" t="n">
-        <v>5.3</v>
+        <v>2.48</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.79</v>
+        <v>2.56</v>
       </c>
       <c r="BF91" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BG91" t="n">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="BH91" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI91" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ91" t="n">
         <v>1000</v>
       </c>
       <c r="BK91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BL91" t="n">
         <v>1000</v>
       </c>
       <c r="BM91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BN91" t="n">
         <v>1000</v>
       </c>
       <c r="BO91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BP91" t="n">
         <v>1000</v>
       </c>
       <c r="BQ91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BR91" t="n">
         <v>1000</v>
       </c>
       <c r="BS91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BT91" t="n">
         <v>1000</v>
       </c>
       <c r="BU91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BV91" t="n">
         <v>1000</v>
       </c>
       <c r="BW91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BX91" t="n">
         <v>1000</v>
       </c>
       <c r="BY91" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BZ91" t="n">
         <v>0</v>
@@ -23686,7 +23686,7 @@
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -23723,7 +23723,7 @@
         <v>2.08</v>
       </c>
       <c r="H92" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I92" t="n">
         <v>4.8</v>
@@ -23732,7 +23732,7 @@
         <v>3.4</v>
       </c>
       <c r="K92" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
@@ -23940,7 +23940,7 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
         <v>3.25</v>
       </c>
       <c r="G93" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H93" t="n">
         <v>2.18</v>
@@ -23989,7 +23989,7 @@
         <v>3.85</v>
       </c>
       <c r="L93" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M93" t="n">
         <v>1.07</v>
@@ -24004,7 +24004,7 @@
         <v>1.88</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R93" t="n">
         <v>1.35</v>
@@ -24094,7 +24094,7 @@
         <v>10</v>
       </c>
       <c r="AU93" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV93" t="n">
         <v>8.6</v>
@@ -24118,10 +24118,10 @@
         <v>1.03</v>
       </c>
       <c r="BC93" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BD93" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="BE93" t="n">
         <v>1.03</v>
@@ -24194,7 +24194,7 @@
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
       </c>
       <c r="CB94" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
         <v>13.5</v>
       </c>
       <c r="AW95" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX95" t="n">
         <v>9</v>
@@ -24638,7 +24638,7 @@
         <v>6.6</v>
       </c>
       <c r="BG95" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH95" t="n">
         <v>4.2</v>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="CB95" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -24739,7 +24739,7 @@
         <v>3.1</v>
       </c>
       <c r="H96" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I96" t="n">
         <v>2.92</v>
@@ -24757,7 +24757,7 @@
         <v>1.09</v>
       </c>
       <c r="N96" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O96" t="n">
         <v>1.4</v>
@@ -24769,13 +24769,13 @@
         <v>2.16</v>
       </c>
       <c r="R96" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
       </c>
       <c r="T96" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U96" t="n">
         <v>2</v>
@@ -24916,7 +24916,7 @@
         <v>5.9</v>
       </c>
       <c r="BO96" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP96" t="n">
         <v>1000</v>
@@ -24928,7 +24928,7 @@
         <v>1000</v>
       </c>
       <c r="BS96" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT96" t="n">
         <v>5.7</v>
@@ -24940,7 +24940,7 @@
         <v>1000</v>
       </c>
       <c r="BW96" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX96" t="n">
         <v>1000</v>
@@ -24952,11 +24952,11 @@
         <v>1000</v>
       </c>
       <c r="CA96" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB96" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G97" t="n">
         <v>3.15</v>
@@ -24996,13 +24996,13 @@
         <v>2.58</v>
       </c>
       <c r="I97" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J97" t="n">
         <v>3.3</v>
       </c>
       <c r="K97" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L97" t="n">
         <v>1.37</v>
@@ -25011,16 +25011,16 @@
         <v>1.08</v>
       </c>
       <c r="N97" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O97" t="n">
         <v>1.37</v>
       </c>
       <c r="P97" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R97" t="n">
         <v>1.29</v>
@@ -25029,13 +25029,13 @@
         <v>3.75</v>
       </c>
       <c r="T97" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U97" t="n">
         <v>2.08</v>
       </c>
       <c r="V97" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W97" t="n">
         <v>1.46</v>
@@ -25053,7 +25053,7 @@
         <v>42</v>
       </c>
       <c r="AB97" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC97" t="n">
         <v>9</v>
@@ -25065,7 +25065,7 @@
         <v>34</v>
       </c>
       <c r="AF97" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG97" t="n">
         <v>14</v>
@@ -25104,7 +25104,7 @@
         <v>12.5</v>
       </c>
       <c r="AS97" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT97" t="n">
         <v>8.199999999999999</v>
@@ -25116,7 +25116,7 @@
         <v>9</v>
       </c>
       <c r="AW97" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX97" t="n">
         <v>14.5</v>
@@ -25128,22 +25128,22 @@
         <v>13</v>
       </c>
       <c r="BA97" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB97" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC97" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD97" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE97" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF97" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG97" t="n">
         <v>20</v>
@@ -25210,7 +25210,7 @@
       </c>
       <c r="CB97" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -25253,7 +25253,7 @@
         <v>3.7</v>
       </c>
       <c r="J98" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K98" t="n">
         <v>3.1</v>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="CB98" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25498,7 @@
         <v>2.08</v>
       </c>
       <c r="G99" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H99" t="n">
         <v>3.95</v>
@@ -25510,7 +25510,7 @@
         <v>3.4</v>
       </c>
       <c r="K99" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L99" t="n">
         <v>1.01</v>
@@ -25543,10 +25543,10 @@
         <v>2</v>
       </c>
       <c r="V99" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W99" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X99" t="n">
         <v>14.5</v>
@@ -25561,7 +25561,7 @@
         <v>95</v>
       </c>
       <c r="AB99" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC99" t="n">
         <v>8.199999999999999</v>
@@ -25612,7 +25612,7 @@
         <v>21</v>
       </c>
       <c r="AS99" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT99" t="n">
         <v>6.6</v>
@@ -25624,7 +25624,7 @@
         <v>12</v>
       </c>
       <c r="AW99" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX99" t="n">
         <v>10</v>
@@ -25636,7 +25636,7 @@
         <v>14.5</v>
       </c>
       <c r="BA99" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB99" t="n">
         <v>20</v>
@@ -25645,16 +25645,16 @@
         <v>18.5</v>
       </c>
       <c r="BD99" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE99" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF99" t="n">
         <v>15</v>
       </c>
       <c r="BG99" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH99" t="n">
         <v>1000</v>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="CB99" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
         <v>3.5</v>
       </c>
       <c r="L100" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M100" t="n">
         <v>1.1</v>
@@ -25972,7 +25972,7 @@
       </c>
       <c r="CB100" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -26012,13 +26012,13 @@
         <v>3.9</v>
       </c>
       <c r="I101" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J101" t="n">
         <v>3.65</v>
       </c>
       <c r="K101" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L101" t="n">
         <v>1.34</v>
@@ -26039,7 +26039,7 @@
         <v>1.92</v>
       </c>
       <c r="R101" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S101" t="n">
         <v>3.45</v>
@@ -26051,7 +26051,7 @@
         <v>2.06</v>
       </c>
       <c r="V101" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W101" t="n">
         <v>1.93</v>
@@ -26226,7 +26226,7 @@
       </c>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
@@ -26323,7 +26323,7 @@
         <v>75</v>
       </c>
       <c r="AB102" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC102" t="n">
         <v>8</v>
@@ -26371,7 +26371,7 @@
         <v>7.2</v>
       </c>
       <c r="AR102" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS102" t="n">
         <v>4.9</v>
@@ -26398,10 +26398,10 @@
         <v>17</v>
       </c>
       <c r="BA102" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB102" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BC102" t="n">
         <v>4.7</v>
@@ -26410,10 +26410,10 @@
         <v>4.9</v>
       </c>
       <c r="BE102" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF102" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BG102" t="n">
         <v>4.9</v>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="CB102" t="inlineStr">
         <is>
-          <t>2026-05-30 10:22:09</t>
+          <t>2026-05-30 12:44:29</t>
         </is>
       </c>
     </row>
